--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9EBFC7B-4D5A-4BCC-8B0E-D81EB4C53557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30422DC8-83FF-4DC4-8E32-5425E0346A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="3240" windowWidth="21555" windowHeight="11295" xr2:uid="{9D55B045-82DE-413D-B41F-5DCA56789626}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{11873F4D-6B6C-473D-B515-5F114D05EC28}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -900,7 +900,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D06069-5FFE-4C1E-81F9-410B48481976}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26AF294C-3261-4767-A4BB-7A022C8C8839}">
   <dimension ref="A1:O80"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30422DC8-83FF-4DC4-8E32-5425E0346A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{798F27DA-7352-4B62-8567-053B09BACDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{11873F4D-6B6C-473D-B515-5F114D05EC28}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{07B4FCB3-FF16-4E63-8B27-07285E70AFC4}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="113">
   <si>
     <t>Dados</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
   </si>
   <si>
     <t>02/01/2026</t>
@@ -900,8 +903,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26AF294C-3261-4767-A4BB-7A022C8C8839}">
-  <dimension ref="A1:O80"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CA8AB7-A591-4CD1-85BC-46C85D7EFCC6}">
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -932,14 +935,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -953,40 +956,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1025,25 +1028,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1066,25 +1069,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1107,25 +1110,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1148,25 +1151,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1189,25 +1192,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1230,25 +1233,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1271,25 +1274,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1312,25 +1315,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1353,25 +1356,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1394,25 +1397,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1435,25 +1438,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1476,25 +1479,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1517,25 +1520,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1558,25 +1561,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1599,25 +1602,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1640,25 +1643,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1681,25 +1684,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1722,25 +1725,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1763,25 +1766,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1804,25 +1807,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1845,25 +1848,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1886,25 +1889,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1927,25 +1930,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -1968,25 +1971,25 @@
         <v>46027.4840625</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I27" s="7">
         <v>1404289</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2009,25 +2012,25 @@
         <v>46030.397997685184</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I28" s="7">
         <v>1394724</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2050,25 +2053,25 @@
         <v>46030.408148148148</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I29" s="7">
         <v>1394724</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2091,25 +2094,25 @@
         <v>46030.478854166664</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I30" s="7">
         <v>1394724</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2132,25 +2135,25 @@
         <v>46030.561284722222</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I31" s="7">
         <v>1394724</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2173,25 +2176,25 @@
         <v>46035.478368055556</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I32" s="7">
         <v>1394724</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2214,25 +2217,25 @@
         <v>46043.385474537034</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2255,25 +2258,25 @@
         <v>46043.565196759257</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2296,25 +2299,25 @@
         <v>46069.559953703705</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I35" s="7">
         <v>1421099</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2337,25 +2340,25 @@
         <v>46035.47824074074</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I36" s="7">
         <v>1404958</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2378,25 +2381,25 @@
         <v>46043.385196759256</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I37" s="7">
         <v>1405794</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
@@ -2419,25 +2422,25 @@
         <v>46043.385289351849</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I38" s="7">
         <v>1405794</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
@@ -2460,25 +2463,25 @@
         <v>46043.441296296296</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I39" s="7">
         <v>1405794</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
@@ -2501,25 +2504,25 @@
         <v>46044.570300925923</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I40" s="7">
         <v>1405794</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
@@ -2542,25 +2545,25 @@
         <v>46050.574884259258</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I41" s="7">
         <v>1411351</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
@@ -2583,25 +2586,25 @@
         <v>46051.280300925922</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I42" s="7">
         <v>1411352</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
@@ -2624,25 +2627,25 @@
         <v>46056.33489583333</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I43" s="7">
         <v>1410338</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
@@ -2665,25 +2668,25 @@
         <v>46062.345243055555</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I44" s="7">
         <v>1412987</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
@@ -2706,25 +2709,25 @@
         <v>46064.292500000003</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I45" s="7">
         <v>1412987</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
@@ -2747,25 +2750,25 @@
         <v>46073.402627314812</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I46" s="7">
         <v>1421099</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2832,25 +2835,25 @@
         <v>46027.666331018518</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I49" s="7">
         <v>1386388</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
@@ -2873,25 +2876,25 @@
         <v>46027.694131944445</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I50" s="7">
         <v>1386388</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
@@ -2914,25 +2917,25 @@
         <v>46036.841574074075</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I51" s="7">
         <v>1406206</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
@@ -2955,25 +2958,25 @@
         <v>46059.905682870369</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I52" s="7">
         <v>1411984</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
@@ -2996,25 +2999,25 @@
         <v>46064.60796296296</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I53" s="7">
         <v>1411990</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
@@ -3037,25 +3040,25 @@
         <v>46065.655185185184</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I54" s="7">
         <v>1411990</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
@@ -3078,25 +3081,25 @@
         <v>46066.613657407404</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I55" s="7">
         <v>1411990</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
@@ -3119,25 +3122,25 @@
         <v>46066.670127314814</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I56" s="7">
         <v>1411990</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
@@ -3160,25 +3163,25 @@
         <v>46028.907905092594</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I57" s="7">
         <v>1394721</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
@@ -3201,25 +3204,25 @@
         <v>46029.6719212963</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I58" s="7">
         <v>1394721</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
@@ -3242,25 +3245,25 @@
         <v>46034.72855324074</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I59" s="7">
         <v>1394721</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
@@ -3283,25 +3286,25 @@
         <v>46037.838958333334</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I60" s="7">
         <v>1394721</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
@@ -3324,25 +3327,25 @@
         <v>46042.727754629632</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I61" s="7">
         <v>1394721</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
@@ -3365,25 +3368,25 @@
         <v>46043.627881944441</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I62" s="7">
         <v>1410339</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
@@ -3406,25 +3409,25 @@
         <v>46052.626018518517</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I63" s="7">
         <v>1411706</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
@@ -3447,25 +3450,25 @@
         <v>46053.632291666669</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I64" s="7">
         <v>1411708</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
@@ -3488,25 +3491,25 @@
         <v>46071.601446759261</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I65" s="7">
         <v>1418251</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
@@ -3517,41 +3520,41 @@
     <row r="66" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D66" s="8">
-        <v>46027.633611111109</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E66" s="8">
-        <v>46027.633611111109</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I66" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>79</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O66" s="7"/>
     </row>
@@ -3561,38 +3564,38 @@
         <v>6</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D67" s="8">
-        <v>46029.802372685182</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E67" s="8">
-        <v>46029.802372685182</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I67" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>80</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O67" s="7"/>
     </row>
@@ -3602,19 +3605,19 @@
         <v>6</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D68" s="8">
-        <v>46030.908472222225</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E68" s="8">
-        <v>46030.908472222225</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>66</v>
@@ -3623,17 +3626,17 @@
         <v>1394724</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3643,120 +3646,120 @@
         <v>6</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D69" s="8">
-        <v>46031.590057870373</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E69" s="8">
-        <v>46031.590057870373</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I69" s="7">
         <v>1394724</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O69" s="7"/>
     </row>
     <row r="70" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D70" s="8">
-        <v>46024.795127314814</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E70" s="8">
-        <v>46024.795127314814</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I70" s="7">
-        <v>1398335</v>
+        <v>1394724</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O70" s="7"/>
     </row>
     <row r="71" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>40</v>
       </c>
       <c r="D71" s="8">
-        <v>46024.795277777775</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E71" s="8">
-        <v>46024.795277777775</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I71" s="7">
-        <v>1398335</v>
+        <v>1422286</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3766,38 +3769,38 @@
         <v>7</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D72" s="8">
-        <v>46024.900324074071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E72" s="8">
-        <v>46024.900324074071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I72" s="7">
         <v>1398335</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O72" s="7"/>
     </row>
@@ -3807,34 +3810,34 @@
         <v>7</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D73" s="8">
-        <v>46028.866898148146</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E73" s="8">
-        <v>46028.866898148146</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H73" s="5" t="s">
         <v>66</v>
       </c>
       <c r="I73" s="7">
-        <v>1402956</v>
+        <v>1398335</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
@@ -3848,38 +3851,38 @@
         <v>7</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D74" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E74" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I74" s="7">
-        <v>1404958</v>
+        <v>1398335</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3889,38 +3892,38 @@
         <v>7</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D75" s="8">
-        <v>46062.904895833337</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E75" s="8">
-        <v>46062.904895833337</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I75" s="7">
-        <v>1412987</v>
+        <v>1402956</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3930,38 +3933,38 @@
         <v>7</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D76" s="8">
-        <v>46063.874467592592</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E76" s="8">
-        <v>46063.874467592592</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I76" s="7">
-        <v>1412987</v>
+        <v>1404958</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -3971,38 +3974,38 @@
         <v>7</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D77" s="8">
-        <v>46067.906875000001</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E77" s="8">
-        <v>46067.906875000001</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I77" s="7">
-        <v>1411991</v>
+        <v>1412987</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O77" s="7"/>
     </row>
@@ -4012,87 +4015,169 @@
         <v>7</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D78" s="8">
-        <v>46069.700543981482</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E78" s="8">
-        <v>46069.700543981482</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I78" s="7">
-        <v>1411991</v>
+        <v>1412987</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
+        <v>5</v>
+      </c>
+      <c r="O78" s="7"/>
+    </row>
+    <row r="79" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A79" s="2"/>
+      <c r="B79" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E79" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I79" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L79" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10">
+        <v>3</v>
+      </c>
+      <c r="O79" s="7"/>
+    </row>
+    <row r="80" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A80" s="2"/>
+      <c r="B80" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E80" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I80" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K80" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10">
         <v>10</v>
       </c>
-      <c r="O78" s="7"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A79" s="4"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="6"/>
-      <c r="L79" s="6"/>
-      <c r="M79" s="9">
+      <c r="O80" s="7"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A81" s="4"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="9">
         <v>0</v>
       </c>
-      <c r="N79" s="9">
-        <v>144</v>
-      </c>
-      <c r="O79" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="9">
-        <v>73</v>
-      </c>
-      <c r="I80" s="6"/>
-      <c r="J80" s="6"/>
-      <c r="K80" s="6"/>
-      <c r="L80" s="6"/>
-      <c r="M80" s="9">
+      <c r="N81" s="9">
+        <v>160</v>
+      </c>
+      <c r="O81" s="9">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="9">
+        <v>75</v>
+      </c>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="9">
         <v>0</v>
       </c>
-      <c r="N80" s="9">
-        <v>339</v>
-      </c>
-      <c r="O80" s="9">
-        <v>73</v>
+      <c r="N82" s="9">
+        <v>355</v>
+      </c>
+      <c r="O82" s="9">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{798F27DA-7352-4B62-8567-053B09BACDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF00A9EC-A8C0-41AA-8345-FC909CFD9F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{07B4FCB3-FF16-4E63-8B27-07285E70AFC4}"/>
+    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{F406952C-5FB2-4B25-BBFE-996FA6F356DB}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="114">
   <si>
     <t>Dados</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
   </si>
   <si>
     <t>05/01/2026</t>
@@ -903,8 +906,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CA8AB7-A591-4CD1-85BC-46C85D7EFCC6}">
-  <dimension ref="A1:O82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ADE1002-6B5E-4CC2-89CC-99B3A2A3AACB}">
+  <dimension ref="A1:O88"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -935,14 +938,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -956,40 +959,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1028,25 +1031,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1069,25 +1072,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1110,25 +1113,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1151,25 +1154,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1192,25 +1195,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1233,25 +1236,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1274,25 +1277,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1315,25 +1318,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1356,25 +1359,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1397,25 +1400,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1438,25 +1441,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1479,25 +1482,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1520,25 +1523,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1561,25 +1564,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1602,25 +1605,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1643,25 +1646,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1684,25 +1687,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1725,25 +1728,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1766,25 +1769,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1807,25 +1810,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1848,25 +1851,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1889,25 +1892,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1930,25 +1933,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -1959,28 +1962,28 @@
     <row r="27" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="8">
-        <v>46027.4840625</v>
+        <v>46077.38318287037</v>
       </c>
       <c r="E27" s="8">
-        <v>46027.4840625</v>
+        <v>46077.38318287037</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I27" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>80</v>
@@ -1989,11 +1992,11 @@
         <v>97</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O27" s="7"/>
     </row>
@@ -2003,38 +2006,38 @@
         <v>6</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D28" s="8">
-        <v>46030.397997685184</v>
+        <v>46027.4840625</v>
       </c>
       <c r="E28" s="8">
-        <v>46030.397997685184</v>
+        <v>46027.4840625</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I28" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>81</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O28" s="7"/>
     </row>
@@ -2047,31 +2050,31 @@
         <v>17</v>
       </c>
       <c r="D29" s="8">
-        <v>46030.408148148148</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="E29" s="8">
-        <v>46030.408148148148</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I29" s="7">
         <v>1394724</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2088,31 +2091,31 @@
         <v>17</v>
       </c>
       <c r="D30" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="E30" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I30" s="7">
         <v>1394724</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2129,35 +2132,35 @@
         <v>17</v>
       </c>
       <c r="D31" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="E31" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I31" s="7">
         <v>1394724</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O31" s="7"/>
     </row>
@@ -2167,38 +2170,38 @@
         <v>6</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D32" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="E32" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>48</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I32" s="7">
         <v>1394724</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O32" s="7"/>
     </row>
@@ -2208,38 +2211,38 @@
         <v>6</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D33" s="8">
-        <v>46043.385474537034</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="E33" s="8">
-        <v>46043.385474537034</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O33" s="7"/>
     </row>
@@ -2249,34 +2252,34 @@
         <v>6</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D34" s="8">
-        <v>46043.565196759257</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="E34" s="8">
-        <v>46043.565196759257</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2293,22 +2296,22 @@
         <v>27</v>
       </c>
       <c r="D35" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="E35" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I35" s="7">
-        <v>1421099</v>
+        <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>82</v>
@@ -2317,52 +2320,52 @@
         <v>97</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O35" s="7"/>
     </row>
     <row r="36" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D36" s="8">
-        <v>46035.47824074074</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="E36" s="8">
-        <v>46035.47824074074</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>48</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I36" s="7">
-        <v>1404958</v>
+        <v>1421099</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O36" s="7"/>
     </row>
@@ -2372,38 +2375,38 @@
         <v>7</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D37" s="8">
-        <v>46043.385196759256</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E37" s="8">
-        <v>46043.385196759256</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I37" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>84</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O37" s="7"/>
     </row>
@@ -2413,19 +2416,19 @@
         <v>7</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D38" s="8">
-        <v>46043.385289351849</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E38" s="8">
-        <v>46043.385289351849</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>67</v>
@@ -2434,17 +2437,17 @@
         <v>1405794</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O38" s="7"/>
     </row>
@@ -2454,38 +2457,38 @@
         <v>7</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E39" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I39" s="7">
         <v>1405794</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O39" s="7"/>
     </row>
@@ -2495,38 +2498,38 @@
         <v>7</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D40" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E40" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I40" s="7">
         <v>1405794</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O40" s="7"/>
     </row>
@@ -2536,38 +2539,38 @@
         <v>7</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D41" s="8">
-        <v>46050.574884259258</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E41" s="8">
-        <v>46050.574884259258</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I41" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O41" s="7"/>
     </row>
@@ -2577,38 +2580,38 @@
         <v>7</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" s="8">
-        <v>46051.280300925922</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E42" s="8">
-        <v>46051.280300925922</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I42" s="7">
-        <v>1411352</v>
+        <v>1411351</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>86</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>106</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O42" s="7"/>
     </row>
@@ -2618,38 +2621,38 @@
         <v>7</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D43" s="8">
-        <v>46056.33489583333</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E43" s="8">
-        <v>46056.33489583333</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>53</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I43" s="7">
-        <v>1410338</v>
+        <v>1411352</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O43" s="7"/>
     </row>
@@ -2659,38 +2662,38 @@
         <v>7</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D44" s="8">
-        <v>46062.345243055555</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E44" s="8">
-        <v>46062.345243055555</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I44" s="7">
-        <v>1412987</v>
+        <v>1410338</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>88</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O44" s="7"/>
     </row>
@@ -2700,38 +2703,38 @@
         <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D45" s="8">
-        <v>46064.292500000003</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E45" s="8">
-        <v>46064.292500000003</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I45" s="7">
         <v>1412987</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O45" s="7"/>
     </row>
@@ -2741,119 +2744,157 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D46" s="8">
-        <v>46073.402627314812</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E46" s="8">
-        <v>46073.402627314812</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I46" s="7">
-        <v>1421099</v>
+        <v>1412987</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
+        <v>3</v>
+      </c>
+      <c r="O46" s="7"/>
+    </row>
+    <row r="47" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A47" s="2"/>
+      <c r="B47" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="8">
+        <v>46073.402627314812</v>
+      </c>
+      <c r="E47" s="8">
+        <v>46073.402627314812</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I47" s="7">
+        <v>1421099</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10">
         <v>2</v>
       </c>
-      <c r="O46" s="7"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A47" s="4"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="9">
-        <v>0</v>
-      </c>
-      <c r="N47" s="9">
-        <v>195</v>
-      </c>
-      <c r="O47" s="9">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="12"/>
+      <c r="O47" s="7"/>
+    </row>
+    <row r="48" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A48" s="2"/>
+      <c r="B48" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="E48" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I48" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10">
+        <v>3</v>
+      </c>
+      <c r="O48" s="7"/>
     </row>
     <row r="49" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D49" s="8">
-        <v>46027.666331018518</v>
+        <v>46077.554594907408</v>
       </c>
       <c r="E49" s="8">
-        <v>46027.666331018518</v>
+        <v>46077.554594907408</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>64</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I49" s="7">
-        <v>1386388</v>
+        <v>1422285</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K49" s="5" t="s">
         <v>98</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
@@ -2861,87 +2902,49 @@
       </c>
       <c r="O49" s="7"/>
     </row>
-    <row r="50" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A50" s="2"/>
-      <c r="B50" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E50" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I50" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K50" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10">
-        <v>1</v>
-      </c>
-      <c r="O50" s="7"/>
-    </row>
-    <row r="51" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="E51" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I51" s="7">
-        <v>1406206</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K51" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="L51" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10">
-        <v>11</v>
-      </c>
-      <c r="O51" s="7"/>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50" s="4"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="9">
+        <v>0</v>
+      </c>
+      <c r="N50" s="9">
+        <v>203</v>
+      </c>
+      <c r="O50" s="9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
+      <c r="O51" s="12"/>
     </row>
     <row r="52" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
@@ -2949,38 +2952,38 @@
         <v>4</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D52" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E52" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I52" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O52" s="7"/>
     </row>
@@ -2990,38 +2993,38 @@
         <v>4</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D53" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E53" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I53" s="7">
-        <v>1411990</v>
+        <v>1386388</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L53" s="7" t="s">
         <v>102</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53" s="7"/>
     </row>
@@ -3031,38 +3034,38 @@
         <v>4</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D54" s="8">
-        <v>46065.655185185184</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E54" s="8">
-        <v>46065.655185185184</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I54" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O54" s="7"/>
     </row>
@@ -3072,38 +3075,38 @@
         <v>4</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D55" s="8">
-        <v>46066.613657407404</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E55" s="8">
-        <v>46066.613657407404</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>58</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I55" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O55" s="7"/>
     </row>
@@ -3113,34 +3116,34 @@
         <v>4</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D56" s="8">
-        <v>46066.670127314814</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E56" s="8">
-        <v>46066.670127314814</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I56" s="7">
         <v>1411990</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
@@ -3151,123 +3154,123 @@
     <row r="57" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D57" s="8">
-        <v>46028.907905092594</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E57" s="8">
-        <v>46028.907905092594</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I57" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O57" s="7"/>
     </row>
     <row r="58" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D58" s="8">
-        <v>46029.6719212963</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E58" s="8">
-        <v>46029.6719212963</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I58" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O58" s="7"/>
     </row>
     <row r="59" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D59" s="8">
-        <v>46034.72855324074</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E59" s="8">
-        <v>46034.72855324074</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I59" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O59" s="7"/>
     </row>
@@ -3277,38 +3280,38 @@
         <v>5</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D60" s="8">
-        <v>46037.838958333334</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E60" s="8">
-        <v>46037.838958333334</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I60" s="7">
         <v>1394721</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O60" s="7"/>
     </row>
@@ -3318,38 +3321,38 @@
         <v>5</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D61" s="8">
-        <v>46042.727754629632</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E61" s="8">
-        <v>46042.727754629632</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I61" s="7">
         <v>1394721</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O61" s="7"/>
     </row>
@@ -3359,38 +3362,38 @@
         <v>5</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D62" s="8">
-        <v>46043.627881944441</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E62" s="8">
-        <v>46043.627881944441</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I62" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O62" s="7"/>
     </row>
@@ -3400,38 +3403,38 @@
         <v>5</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D63" s="8">
-        <v>46052.626018518517</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E63" s="8">
-        <v>46052.626018518517</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I63" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>76</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O63" s="7"/>
     </row>
@@ -3441,38 +3444,38 @@
         <v>5</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D64" s="8">
-        <v>46053.632291666669</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E64" s="8">
-        <v>46053.632291666669</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I64" s="7">
-        <v>1411708</v>
+        <v>1394721</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O64" s="7"/>
     </row>
@@ -3482,34 +3485,34 @@
         <v>5</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D65" s="8">
-        <v>46071.601446759261</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E65" s="8">
-        <v>46071.601446759261</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I65" s="7">
-        <v>1418251</v>
+        <v>1410339</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
@@ -3523,198 +3526,198 @@
         <v>5</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D66" s="8">
-        <v>46076.679282407407</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E66" s="8">
-        <v>46076.679282407407</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I66" s="7">
-        <v>1422511</v>
+        <v>1411706</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O66" s="7"/>
     </row>
     <row r="67" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D67" s="8">
-        <v>46027.633611111109</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E67" s="8">
-        <v>46027.633611111109</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I67" s="7">
-        <v>1404289</v>
+        <v>1411708</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K67" s="5" t="s">
         <v>99</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O67" s="7"/>
     </row>
     <row r="68" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D68" s="8">
-        <v>46029.802372685182</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E68" s="8">
-        <v>46029.802372685182</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I68" s="7">
-        <v>1394724</v>
+        <v>1418251</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O68" s="7"/>
     </row>
     <row r="69" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D69" s="8">
-        <v>46030.908472222225</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E69" s="8">
-        <v>46030.908472222225</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I69" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O69" s="7"/>
     </row>
     <row r="70" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D70" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E70" s="8">
-        <v>46031.590057870373</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I70" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
@@ -3725,160 +3728,160 @@
     <row r="71" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D71" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E71" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I71" s="7">
-        <v>1422286</v>
+        <v>1422511</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O71" s="7"/>
     </row>
     <row r="72" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D72" s="8">
-        <v>46024.795127314814</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E72" s="8">
-        <v>46024.795127314814</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H72" s="5" t="s">
         <v>67</v>
       </c>
       <c r="I72" s="7">
-        <v>1398335</v>
+        <v>1404289</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O72" s="7"/>
     </row>
     <row r="73" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D73" s="8">
-        <v>46024.795277777775</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E73" s="8">
-        <v>46024.795277777775</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I73" s="7">
-        <v>1398335</v>
+        <v>1394724</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O73" s="7"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D74" s="8">
-        <v>46024.900324074071</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E74" s="8">
-        <v>46024.900324074071</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I74" s="7">
-        <v>1398335</v>
+        <v>1394724</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
@@ -3889,82 +3892,82 @@
     <row r="75" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D75" s="8">
-        <v>46028.866898148146</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E75" s="8">
-        <v>46028.866898148146</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I75" s="7">
-        <v>1402956</v>
+        <v>1394724</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O75" s="7"/>
     </row>
     <row r="76" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D76" s="8">
-        <v>46034.751261574071</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E76" s="8">
-        <v>46034.751261574071</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I76" s="7">
-        <v>1404958</v>
+        <v>1422286</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -3974,38 +3977,38 @@
         <v>7</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D77" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E77" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I77" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O77" s="7"/>
     </row>
@@ -4018,35 +4021,35 @@
         <v>42</v>
       </c>
       <c r="D78" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E78" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I78" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O78" s="7"/>
     </row>
@@ -4056,38 +4059,38 @@
         <v>7</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D79" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E79" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I79" s="7">
-        <v>1411991</v>
+        <v>1398335</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>94</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4097,87 +4100,333 @@
         <v>7</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D80" s="8">
-        <v>46069.700543981482</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E80" s="8">
-        <v>46069.700543981482</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I80" s="7">
-        <v>1411991</v>
+        <v>1402956</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
+        <v>2</v>
+      </c>
+      <c r="O80" s="7"/>
+    </row>
+    <row r="81" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A81" s="2"/>
+      <c r="B81" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D81" s="8">
+        <v>46034.751261574071</v>
+      </c>
+      <c r="E81" s="8">
+        <v>46034.751261574071</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I81" s="7">
+        <v>1404958</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10">
+        <v>7</v>
+      </c>
+      <c r="O81" s="7"/>
+    </row>
+    <row r="82" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A82" s="2"/>
+      <c r="B82" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" s="8">
+        <v>46062.904895833337</v>
+      </c>
+      <c r="E82" s="8">
+        <v>46062.904895833337</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I82" s="7">
+        <v>1412987</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K82" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10">
+        <v>1</v>
+      </c>
+      <c r="O82" s="7"/>
+    </row>
+    <row r="83" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A83" s="2"/>
+      <c r="B83" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D83" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="E83" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I83" s="7">
+        <v>1412987</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K83" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L83" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10">
+        <v>5</v>
+      </c>
+      <c r="O83" s="7"/>
+    </row>
+    <row r="84" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A84" s="2"/>
+      <c r="B84" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E84" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I84" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K84" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L84" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10">
+        <v>3</v>
+      </c>
+      <c r="O84" s="7"/>
+    </row>
+    <row r="85" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A85" s="2"/>
+      <c r="B85" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D85" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E85" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I85" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K85" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L85" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="M85" s="10"/>
+      <c r="N85" s="10">
         <v>10</v>
       </c>
-      <c r="O80" s="7"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A81" s="4"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="9">
+      <c r="O85" s="7"/>
+    </row>
+    <row r="86" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A86" s="2"/>
+      <c r="B86" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E86" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I86" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L86" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M86" s="10"/>
+      <c r="N86" s="10">
+        <v>1</v>
+      </c>
+      <c r="O86" s="7"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A87" s="4"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="9">
         <v>0</v>
       </c>
-      <c r="N81" s="9">
-        <v>160</v>
-      </c>
-      <c r="O81" s="9">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="9">
-        <v>75</v>
-      </c>
-      <c r="I82" s="6"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
-      <c r="L82" s="6"/>
-      <c r="M82" s="9">
+      <c r="N87" s="9">
+        <v>177</v>
+      </c>
+      <c r="O87" s="9">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A88" s="4"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="9">
+        <v>81</v>
+      </c>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="9">
         <v>0</v>
       </c>
-      <c r="N82" s="9">
-        <v>355</v>
-      </c>
-      <c r="O82" s="9">
-        <v>75</v>
+      <c r="N88" s="9">
+        <v>380</v>
+      </c>
+      <c r="O88" s="9">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -4187,8 +4436,9 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B48:O48"/>
+    <mergeCell ref="B51:O51"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF00A9EC-A8C0-41AA-8345-FC909CFD9F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ACBB0B4-B29D-4E49-AD2B-30040C0A7227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{F406952C-5FB2-4B25-BBFE-996FA6F356DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{526FF178-A934-43D6-B9D8-8B88739B81CC}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="115">
   <si>
     <t>Dados</t>
   </si>
@@ -100,6 +100,9 @@
     <t>24/02/2026</t>
   </si>
   <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
     <t>05/01/2026</t>
   </si>
   <si>
@@ -274,6 +277,9 @@
     <t>CIPF002325-URSA-2023-24 - GARRAFA CILINDRICA DEC 480ML - IMPRESSÃO</t>
   </si>
   <si>
+    <t xml:space="preserve">CI003141-EM-CASA-961 - COPO CAFÉ FACETADO C/ IMPRESSÃO DIGITAL </t>
+  </si>
+  <si>
     <t>CIPF002816STITCHCAP2624 - CORPO GARRAFA FUN 600 ML - STITCH CAPIVA</t>
   </si>
   <si>
@@ -283,9 +289,6 @@
     <t xml:space="preserve">CI003141-EM-CASA-1388 - COPO CAFÉ FACETADO C/ IMPRESSÃO DIGITAL </t>
   </si>
   <si>
-    <t xml:space="preserve">CI003141-EM-CASA-961 - COPO CAFÉ FACETADO C/ IMPRESSÃO DIGITAL </t>
-  </si>
-  <si>
     <t xml:space="preserve">CI002027-ARIEL_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - ARIEL </t>
   </si>
   <si>
@@ -340,10 +343,10 @@
     <t>1206</t>
   </si>
   <si>
+    <t>961</t>
+  </si>
+  <si>
     <t>1388</t>
-  </si>
-  <si>
-    <t>961</t>
   </si>
   <si>
     <t>732</t>
@@ -906,8 +909,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ADE1002-6B5E-4CC2-89CC-99B3A2A3AACB}">
-  <dimension ref="A1:O88"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F83709-11EB-4BA4-8AF8-634A59E7FA40}">
+  <dimension ref="A1:O92"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -938,14 +941,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -959,40 +962,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1031,25 +1034,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1072,25 +1075,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1113,25 +1116,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1154,25 +1157,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1195,25 +1198,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1236,25 +1239,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1277,25 +1280,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1318,25 +1321,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1359,25 +1362,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1400,25 +1403,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1441,25 +1444,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1482,25 +1485,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1523,25 +1526,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1564,25 +1567,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1605,25 +1608,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1646,25 +1649,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1687,25 +1690,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1728,25 +1731,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1769,25 +1772,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1810,25 +1813,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1851,25 +1854,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1892,25 +1895,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1933,25 +1936,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -1974,25 +1977,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2003,28 +2006,28 @@
     <row r="28" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D28" s="8">
-        <v>46027.4840625</v>
+        <v>46078.372766203705</v>
       </c>
       <c r="E28" s="8">
-        <v>46027.4840625</v>
+        <v>46078.372766203705</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I28" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>81</v>
@@ -2033,11 +2036,11 @@
         <v>98</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O28" s="7"/>
     </row>
@@ -2047,38 +2050,38 @@
         <v>6</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D29" s="8">
-        <v>46030.397997685184</v>
+        <v>46027.4840625</v>
       </c>
       <c r="E29" s="8">
-        <v>46030.397997685184</v>
+        <v>46027.4840625</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I29" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>82</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O29" s="7"/>
     </row>
@@ -2091,31 +2094,31 @@
         <v>17</v>
       </c>
       <c r="D30" s="8">
-        <v>46030.408148148148</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="E30" s="8">
-        <v>46030.408148148148</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I30" s="7">
         <v>1394724</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2132,31 +2135,31 @@
         <v>17</v>
       </c>
       <c r="D31" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="E31" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I31" s="7">
         <v>1394724</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2173,35 +2176,35 @@
         <v>17</v>
       </c>
       <c r="D32" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="E32" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I32" s="7">
         <v>1394724</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O32" s="7"/>
     </row>
@@ -2211,38 +2214,38 @@
         <v>6</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D33" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="E33" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O33" s="7"/>
     </row>
@@ -2252,38 +2255,38 @@
         <v>6</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D34" s="8">
-        <v>46043.385474537034</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="E34" s="8">
-        <v>46043.385474537034</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O34" s="7"/>
     </row>
@@ -2293,34 +2296,34 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35" s="8">
-        <v>46043.565196759257</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="E35" s="8">
-        <v>46043.565196759257</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2337,22 +2340,22 @@
         <v>28</v>
       </c>
       <c r="D36" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="E36" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I36" s="7">
-        <v>1421099</v>
+        <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>83</v>
@@ -2361,80 +2364,80 @@
         <v>98</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O36" s="7"/>
     </row>
     <row r="37" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D37" s="8">
-        <v>46035.47824074074</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="E37" s="8">
-        <v>46035.47824074074</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>49</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I37" s="7">
-        <v>1404958</v>
+        <v>1421099</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>84</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O37" s="7"/>
     </row>
     <row r="38" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D38" s="8">
-        <v>46043.385196759256</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="E38" s="8">
-        <v>46043.385196759256</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I38" s="7">
-        <v>1405794</v>
+        <v>1422286</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>85</v>
@@ -2443,11 +2446,11 @@
         <v>98</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O38" s="7"/>
     </row>
@@ -2457,38 +2460,38 @@
         <v>7</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D39" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E39" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>68</v>
       </c>
       <c r="I39" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O39" s="7"/>
     </row>
@@ -2498,38 +2501,38 @@
         <v>7</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E40" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I40" s="7">
         <v>1405794</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O40" s="7"/>
     </row>
@@ -2539,34 +2542,34 @@
         <v>7</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D41" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E41" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I41" s="7">
         <v>1405794</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
@@ -2580,38 +2583,38 @@
         <v>7</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D42" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E42" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>48</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I42" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O42" s="7"/>
     </row>
@@ -2621,38 +2624,38 @@
         <v>7</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D43" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E43" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I43" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>87</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O43" s="7"/>
     </row>
@@ -2662,38 +2665,38 @@
         <v>7</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D44" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E44" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I44" s="7">
-        <v>1410338</v>
+        <v>1411351</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>88</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O44" s="7"/>
     </row>
@@ -2703,38 +2706,38 @@
         <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D45" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E45" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>54</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I45" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O45" s="7"/>
     </row>
@@ -2744,38 +2747,38 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D46" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E46" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I46" s="7">
-        <v>1412987</v>
+        <v>1410338</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>89</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O46" s="7"/>
     </row>
@@ -2785,38 +2788,38 @@
         <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D47" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E47" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I47" s="7">
-        <v>1421099</v>
+        <v>1412987</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O47" s="7"/>
     </row>
@@ -2826,34 +2829,34 @@
         <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D48" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E48" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I48" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
@@ -2867,166 +2870,166 @@
         <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="E49" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I49" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
+        <v>2</v>
+      </c>
+      <c r="O49" s="7"/>
+    </row>
+    <row r="50" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A50" s="2"/>
+      <c r="B50" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="E50" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I50" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10">
         <v>3</v>
       </c>
-      <c r="O49" s="7"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A50" s="4"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="9">
+      <c r="O50" s="7"/>
+    </row>
+    <row r="51" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A51" s="2"/>
+      <c r="B51" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="E51" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I51" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10">
+        <v>3</v>
+      </c>
+      <c r="O51" s="7"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A52" s="4"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="9">
         <v>0</v>
       </c>
-      <c r="N50" s="9">
-        <v>203</v>
-      </c>
-      <c r="O50" s="9">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
+      <c r="N52" s="9">
+        <v>212</v>
+      </c>
+      <c r="O52" s="9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B53" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="12"/>
-    </row>
-    <row r="52" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A52" s="2"/>
-      <c r="B52" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="E52" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I52" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L52" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10">
-        <v>3</v>
-      </c>
-      <c r="O52" s="7"/>
-    </row>
-    <row r="53" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A53" s="2"/>
-      <c r="B53" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E53" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H53" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I53" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L53" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10">
-        <v>1</v>
-      </c>
-      <c r="O53" s="7"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="12"/>
     </row>
     <row r="54" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
@@ -3034,38 +3037,38 @@
         <v>4</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D54" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E54" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I54" s="7">
-        <v>1406206</v>
+        <v>1386388</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O54" s="7"/>
     </row>
@@ -3075,38 +3078,38 @@
         <v>4</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D55" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E55" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I55" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O55" s="7"/>
     </row>
@@ -3116,38 +3119,38 @@
         <v>4</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D56" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E56" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I56" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O56" s="7"/>
     </row>
@@ -3160,35 +3163,35 @@
         <v>33</v>
       </c>
       <c r="D57" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E57" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I57" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O57" s="7"/>
     </row>
@@ -3198,38 +3201,38 @@
         <v>4</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D58" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E58" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I58" s="7">
         <v>1411990</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" s="7"/>
     </row>
@@ -3242,31 +3245,31 @@
         <v>34</v>
       </c>
       <c r="D59" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E59" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I59" s="7">
         <v>1411990</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
@@ -3277,82 +3280,82 @@
     <row r="60" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D60" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E60" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I60" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O60" s="7"/>
     </row>
     <row r="61" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D61" s="8">
-        <v>46029.6719212963</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E61" s="8">
-        <v>46029.6719212963</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I61" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O61" s="7"/>
     </row>
@@ -3362,38 +3365,38 @@
         <v>5</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D62" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E62" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I62" s="7">
         <v>1394721</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O62" s="7"/>
     </row>
@@ -3403,38 +3406,38 @@
         <v>5</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D63" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E63" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I63" s="7">
         <v>1394721</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O63" s="7"/>
     </row>
@@ -3444,38 +3447,38 @@
         <v>5</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D64" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E64" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I64" s="7">
         <v>1394721</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O64" s="7"/>
     </row>
@@ -3485,38 +3488,38 @@
         <v>5</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D65" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E65" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I65" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O65" s="7"/>
     </row>
@@ -3529,35 +3532,35 @@
         <v>39</v>
       </c>
       <c r="D66" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E66" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I66" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>77</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" s="7"/>
     </row>
@@ -3567,38 +3570,38 @@
         <v>5</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D67" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E67" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I67" s="7">
-        <v>1411708</v>
+        <v>1410339</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>92</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O67" s="7"/>
     </row>
@@ -3611,35 +3614,35 @@
         <v>40</v>
       </c>
       <c r="D68" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E68" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I68" s="7">
-        <v>1418251</v>
+        <v>1411706</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3649,38 +3652,38 @@
         <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D69" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E69" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I69" s="7">
-        <v>1422511</v>
+        <v>1411708</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O69" s="7"/>
     </row>
@@ -3690,38 +3693,38 @@
         <v>5</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D70" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E70" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I70" s="7">
-        <v>1422511</v>
+        <v>1418251</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3731,120 +3734,120 @@
         <v>5</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D71" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E71" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I71" s="7">
         <v>1422511</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O71" s="7"/>
     </row>
     <row r="72" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D72" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E72" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I72" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>81</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O72" s="7"/>
     </row>
     <row r="73" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D73" s="8">
-        <v>46029.802372685182</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E73" s="8">
-        <v>46029.802372685182</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I73" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3854,38 +3857,38 @@
         <v>6</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D74" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E74" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>68</v>
       </c>
       <c r="I74" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>82</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3895,19 +3898,19 @@
         <v>6</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D75" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E75" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>68</v>
@@ -3916,17 +3919,17 @@
         <v>1394724</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3936,161 +3939,161 @@
         <v>6</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D76" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E76" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I76" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O76" s="7"/>
     </row>
     <row r="77" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D77" s="8">
-        <v>46024.795127314814</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E77" s="8">
-        <v>46024.795127314814</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I77" s="7">
-        <v>1398335</v>
+        <v>1394724</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O77" s="7"/>
     </row>
     <row r="78" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>42</v>
       </c>
       <c r="D78" s="8">
-        <v>46024.795277777775</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E78" s="8">
-        <v>46024.795277777775</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I78" s="7">
-        <v>1398335</v>
+        <v>1422286</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O78" s="7"/>
     </row>
     <row r="79" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D79" s="8">
-        <v>46024.900324074071</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E79" s="8">
-        <v>46024.900324074071</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>58</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>68</v>
       </c>
       <c r="I79" s="7">
-        <v>1398335</v>
+        <v>1422286</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4100,38 +4103,38 @@
         <v>7</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D80" s="8">
-        <v>46028.866898148146</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E80" s="8">
-        <v>46028.866898148146</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I80" s="7">
-        <v>1402956</v>
+        <v>1398335</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O80" s="7"/>
     </row>
@@ -4141,38 +4144,38 @@
         <v>7</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D81" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E81" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I81" s="7">
-        <v>1404958</v>
+        <v>1398335</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O81" s="7"/>
     </row>
@@ -4182,38 +4185,38 @@
         <v>7</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D82" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E82" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I82" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O82" s="7"/>
     </row>
@@ -4223,38 +4226,38 @@
         <v>7</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D83" s="8">
-        <v>46063.874467592592</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E83" s="8">
-        <v>46063.874467592592</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I83" s="7">
-        <v>1412987</v>
+        <v>1402956</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O83" s="7"/>
     </row>
@@ -4264,38 +4267,38 @@
         <v>7</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D84" s="8">
-        <v>46067.906875000001</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E84" s="8">
-        <v>46067.906875000001</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I84" s="7">
-        <v>1411991</v>
+        <v>1404958</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4305,38 +4308,38 @@
         <v>7</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D85" s="8">
-        <v>46069.700543981482</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E85" s="8">
-        <v>46069.700543981482</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I85" s="7">
-        <v>1411991</v>
+        <v>1412987</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4346,87 +4349,251 @@
         <v>7</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D86" s="8">
-        <v>46077.65824074074</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E86" s="8">
-        <v>46077.65824074074</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I86" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
+        <v>5</v>
+      </c>
+      <c r="O86" s="7"/>
+    </row>
+    <row r="87" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A87" s="2"/>
+      <c r="B87" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E87" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I87" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L87" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M87" s="10"/>
+      <c r="N87" s="10">
+        <v>3</v>
+      </c>
+      <c r="O87" s="7"/>
+    </row>
+    <row r="88" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A88" s="2"/>
+      <c r="B88" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E88" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I88" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K88" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L88" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="M88" s="10"/>
+      <c r="N88" s="10">
+        <v>10</v>
+      </c>
+      <c r="O88" s="7"/>
+    </row>
+    <row r="89" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A89" s="2"/>
+      <c r="B89" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E89" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I89" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K89" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L89" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="M89" s="10"/>
+      <c r="N89" s="10">
         <v>1</v>
       </c>
-      <c r="O86" s="7"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A87" s="4"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6"/>
-      <c r="M87" s="9">
+      <c r="O89" s="7"/>
+    </row>
+    <row r="90" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A90" s="2"/>
+      <c r="B90" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E90" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I90" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L90" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="M90" s="10"/>
+      <c r="N90" s="10">
+        <v>1</v>
+      </c>
+      <c r="O90" s="7"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A91" s="4"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="9">
         <v>0</v>
       </c>
-      <c r="N87" s="9">
-        <v>177</v>
-      </c>
-      <c r="O87" s="9">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="9">
-        <v>81</v>
-      </c>
-      <c r="I88" s="6"/>
-      <c r="J88" s="6"/>
-      <c r="K88" s="6"/>
-      <c r="L88" s="6"/>
-      <c r="M88" s="9">
+      <c r="N91" s="9">
+        <v>182</v>
+      </c>
+      <c r="O91" s="9">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A92" s="4"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="9">
+        <v>85</v>
+      </c>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="9">
         <v>0</v>
       </c>
-      <c r="N88" s="9">
-        <v>380</v>
-      </c>
-      <c r="O88" s="9">
-        <v>81</v>
+      <c r="N92" s="9">
+        <v>394</v>
+      </c>
+      <c r="O92" s="9">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -4436,9 +4603,8 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B51:O51"/>
+    <mergeCell ref="B53:O53"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ACBB0B4-B29D-4E49-AD2B-30040C0A7227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD2107F8-81A5-4303-A254-36AF54E01960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{526FF178-A934-43D6-B9D8-8B88739B81CC}"/>
+    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{8EC2283C-B3A0-459D-A031-B95FA7985C31}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="117">
   <si>
     <t>Dados</t>
   </si>
@@ -130,6 +130,9 @@
     <t>13/02/2026</t>
   </si>
   <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
     <t>07/01/2026</t>
   </si>
   <si>
@@ -296,6 +299,9 @@
   </si>
   <si>
     <t>CIPF002816-FITNESS_F-732 - CORPO GARRAFA FUN 600 ML - FITNESS F - I</t>
+  </si>
+  <si>
+    <t>CIPF002259-LIMAO-24 - COPO PEQUENO ROSCA 450 ML C/ IMPRESSÃO D</t>
   </si>
   <si>
     <t>CI002027-MICKEYFUTEBOL24 - CORPO GARRAFA RETRÔ 500ML SOPRO - IMPRES</t>
@@ -909,8 +915,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F83709-11EB-4BA4-8AF8-634A59E7FA40}">
-  <dimension ref="A1:O92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987863C2-E270-4F1A-9430-C8823FDC7009}">
+  <dimension ref="A1:O94"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -941,14 +947,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -962,40 +968,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1034,25 +1040,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1075,25 +1081,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1116,25 +1122,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1157,25 +1163,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1198,25 +1204,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1239,25 +1245,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1280,25 +1286,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1321,25 +1327,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1362,25 +1368,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1403,25 +1409,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1444,25 +1450,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1485,25 +1491,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1526,25 +1532,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1567,25 +1573,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1608,25 +1614,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1649,25 +1655,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1690,25 +1696,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1731,25 +1737,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1772,25 +1778,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1813,25 +1819,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1854,25 +1860,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1895,25 +1901,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1936,25 +1942,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -1977,25 +1983,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2018,25 +2024,25 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2059,25 +2065,25 @@
         <v>46027.4840625</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I29" s="7">
         <v>1404289</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2100,25 +2106,25 @@
         <v>46030.397997685184</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I30" s="7">
         <v>1394724</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2141,25 +2147,25 @@
         <v>46030.408148148148</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I31" s="7">
         <v>1394724</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2182,25 +2188,25 @@
         <v>46030.478854166664</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I32" s="7">
         <v>1394724</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2223,25 +2229,25 @@
         <v>46030.561284722222</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2264,25 +2270,25 @@
         <v>46035.478368055556</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2305,25 +2311,25 @@
         <v>46043.385474537034</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2346,25 +2352,25 @@
         <v>46043.565196759257</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2387,25 +2393,25 @@
         <v>46069.559953703705</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I37" s="7">
         <v>1421099</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
@@ -2428,25 +2434,25 @@
         <v>46078.552407407406</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I38" s="7">
         <v>1422286</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
@@ -2469,25 +2475,25 @@
         <v>46035.47824074074</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I39" s="7">
         <v>1404958</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
@@ -2510,25 +2516,25 @@
         <v>46043.385196759256</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I40" s="7">
         <v>1405794</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
@@ -2551,25 +2557,25 @@
         <v>46043.385289351849</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I41" s="7">
         <v>1405794</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
@@ -2592,25 +2598,25 @@
         <v>46043.441296296296</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I42" s="7">
         <v>1405794</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
@@ -2633,25 +2639,25 @@
         <v>46044.570300925923</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I43" s="7">
         <v>1405794</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
@@ -2674,25 +2680,25 @@
         <v>46050.574884259258</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I44" s="7">
         <v>1411351</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
@@ -2715,25 +2721,25 @@
         <v>46051.280300925922</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I45" s="7">
         <v>1411352</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
@@ -2756,25 +2762,25 @@
         <v>46056.33489583333</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I46" s="7">
         <v>1410338</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2797,25 +2803,25 @@
         <v>46062.345243055555</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I47" s="7">
         <v>1412987</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
@@ -2838,25 +2844,25 @@
         <v>46064.292500000003</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I48" s="7">
         <v>1412987</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
@@ -2879,25 +2885,25 @@
         <v>46073.402627314812</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I49" s="7">
         <v>1421099</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
@@ -2920,25 +2926,25 @@
         <v>46077.368379629632</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I50" s="7">
         <v>1422285</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
@@ -2961,25 +2967,25 @@
         <v>46077.554594907408</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I51" s="7">
         <v>1422285</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
@@ -3046,25 +3052,25 @@
         <v>46027.666331018518</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I54" s="7">
         <v>1386388</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
@@ -3087,25 +3093,25 @@
         <v>46027.694131944445</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I55" s="7">
         <v>1386388</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
@@ -3128,25 +3134,25 @@
         <v>46036.841574074075</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I56" s="7">
         <v>1406206</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
@@ -3169,25 +3175,25 @@
         <v>46059.905682870369</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I57" s="7">
         <v>1411984</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
@@ -3210,25 +3216,25 @@
         <v>46064.60796296296</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I58" s="7">
         <v>1411990</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
@@ -3251,25 +3257,25 @@
         <v>46065.655185185184</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I59" s="7">
         <v>1411990</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
@@ -3292,25 +3298,25 @@
         <v>46066.613657407404</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I60" s="7">
         <v>1411990</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
@@ -3333,25 +3339,25 @@
         <v>46066.670127314814</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I61" s="7">
         <v>1411990</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
@@ -3362,41 +3368,41 @@
     <row r="62" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D62" s="8">
-        <v>46028.907905092594</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E62" s="8">
-        <v>46028.907905092594</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I62" s="7">
-        <v>1394721</v>
+        <v>1410767</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>100</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O62" s="7"/>
     </row>
@@ -3406,38 +3412,38 @@
         <v>5</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D63" s="8">
-        <v>46029.6719212963</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E63" s="8">
-        <v>46029.6719212963</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I63" s="7">
         <v>1394721</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O63" s="7"/>
     </row>
@@ -3450,35 +3456,35 @@
         <v>37</v>
       </c>
       <c r="D64" s="8">
-        <v>46034.72855324074</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E64" s="8">
-        <v>46034.72855324074</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I64" s="7">
         <v>1394721</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O64" s="7"/>
     </row>
@@ -3491,35 +3497,35 @@
         <v>38</v>
       </c>
       <c r="D65" s="8">
-        <v>46037.838958333334</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E65" s="8">
-        <v>46037.838958333334</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I65" s="7">
         <v>1394721</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="O65" s="7"/>
     </row>
@@ -3532,35 +3538,35 @@
         <v>39</v>
       </c>
       <c r="D66" s="8">
-        <v>46042.727754629632</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E66" s="8">
-        <v>46042.727754629632</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I66" s="7">
         <v>1394721</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O66" s="7"/>
     </row>
@@ -3570,34 +3576,34 @@
         <v>5</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D67" s="8">
-        <v>46043.627881944441</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E67" s="8">
-        <v>46043.627881944441</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I67" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
@@ -3611,38 +3617,38 @@
         <v>5</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D68" s="8">
-        <v>46052.626018518517</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E68" s="8">
-        <v>46052.626018518517</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I68" s="7">
-        <v>1411706</v>
+        <v>1410339</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3652,38 +3658,38 @@
         <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D69" s="8">
-        <v>46053.632291666669</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E69" s="8">
-        <v>46053.632291666669</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I69" s="7">
-        <v>1411708</v>
+        <v>1411706</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O69" s="7"/>
     </row>
@@ -3693,38 +3699,38 @@
         <v>5</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D70" s="8">
-        <v>46071.601446759261</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E70" s="8">
-        <v>46071.601446759261</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I70" s="7">
-        <v>1418251</v>
+        <v>1411708</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3737,31 +3743,31 @@
         <v>42</v>
       </c>
       <c r="D71" s="8">
-        <v>46076.679282407407</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E71" s="8">
-        <v>46076.679282407407</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I71" s="7">
-        <v>1422511</v>
+        <v>1418251</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
@@ -3775,38 +3781,38 @@
         <v>5</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D72" s="8">
-        <v>46077.591944444444</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E72" s="8">
-        <v>46077.591944444444</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I72" s="7">
         <v>1422511</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O72" s="7"/>
     </row>
@@ -3819,76 +3825,76 @@
         <v>25</v>
       </c>
       <c r="D73" s="8">
-        <v>46077.861296296294</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E73" s="8">
-        <v>46077.861296296294</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I73" s="7">
         <v>1422511</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O73" s="7"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D74" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E74" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I74" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>82</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3898,38 +3904,38 @@
         <v>6</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D75" s="8">
-        <v>46029.802372685182</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E75" s="8">
-        <v>46029.802372685182</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I75" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3939,19 +3945,19 @@
         <v>6</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D76" s="8">
-        <v>46030.908472222225</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E76" s="8">
-        <v>46030.908472222225</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H76" s="5" t="s">
         <v>69</v>
@@ -3960,17 +3966,17 @@
         <v>1394724</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -3980,38 +3986,38 @@
         <v>6</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D77" s="8">
-        <v>46031.590057870373</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E77" s="8">
-        <v>46031.590057870373</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I77" s="7">
         <v>1394724</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O77" s="7"/>
     </row>
@@ -4021,38 +4027,38 @@
         <v>6</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D78" s="8">
-        <v>46076.8827662037</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E78" s="8">
-        <v>46076.8827662037</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I78" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O78" s="7"/>
     </row>
@@ -4062,79 +4068,79 @@
         <v>6</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D79" s="8">
-        <v>46078.867326388892</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E79" s="8">
-        <v>46078.867326388892</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I79" s="7">
         <v>1422286</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O79" s="7"/>
     </row>
     <row r="80" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D80" s="8">
-        <v>46024.795127314814</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E80" s="8">
-        <v>46024.795127314814</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I80" s="7">
-        <v>1398335</v>
+        <v>1422286</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O80" s="7"/>
     </row>
@@ -4144,38 +4150,38 @@
         <v>7</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D81" s="8">
-        <v>46024.795277777775</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E81" s="8">
-        <v>46024.795277777775</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I81" s="7">
         <v>1398335</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O81" s="7"/>
     </row>
@@ -4185,19 +4191,19 @@
         <v>7</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D82" s="8">
-        <v>46024.900324074071</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E82" s="8">
-        <v>46024.900324074071</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>69</v>
@@ -4206,17 +4212,17 @@
         <v>1398335</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O82" s="7"/>
     </row>
@@ -4226,38 +4232,38 @@
         <v>7</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D83" s="8">
-        <v>46028.866898148146</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E83" s="8">
-        <v>46028.866898148146</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I83" s="7">
-        <v>1402956</v>
+        <v>1398335</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O83" s="7"/>
     </row>
@@ -4267,38 +4273,38 @@
         <v>7</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D84" s="8">
-        <v>46034.751261574071</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E84" s="8">
-        <v>46034.751261574071</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I84" s="7">
-        <v>1404958</v>
+        <v>1402956</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4308,38 +4314,38 @@
         <v>7</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D85" s="8">
-        <v>46062.904895833337</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E85" s="8">
-        <v>46062.904895833337</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I85" s="7">
-        <v>1412987</v>
+        <v>1404958</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4349,38 +4355,38 @@
         <v>7</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D86" s="8">
-        <v>46063.874467592592</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E86" s="8">
-        <v>46063.874467592592</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I86" s="7">
         <v>1412987</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O86" s="7"/>
     </row>
@@ -4390,38 +4396,38 @@
         <v>7</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D87" s="8">
-        <v>46067.906875000001</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E87" s="8">
-        <v>46067.906875000001</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>59</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I87" s="7">
-        <v>1411991</v>
+        <v>1412987</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O87" s="7"/>
     </row>
@@ -4431,38 +4437,38 @@
         <v>7</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D88" s="8">
-        <v>46069.700543981482</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="E88" s="8">
-        <v>46069.700543981482</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I88" s="7">
         <v>1411991</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O88" s="7"/>
     </row>
@@ -4472,38 +4478,38 @@
         <v>7</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D89" s="8">
-        <v>46077.65824074074</v>
+        <v>46069.700543981482</v>
       </c>
       <c r="E89" s="8">
-        <v>46077.65824074074</v>
+        <v>46069.700543981482</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I89" s="7">
-        <v>1422285</v>
+        <v>1411991</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O89" s="7"/>
     </row>
@@ -4513,34 +4519,34 @@
         <v>7</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D90" s="8">
-        <v>46078.881018518521</v>
+        <v>46077.65824074074</v>
       </c>
       <c r="E90" s="8">
-        <v>46078.881018518521</v>
+        <v>46077.65824074074</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I90" s="7">
-        <v>1423123</v>
+        <v>1422285</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
@@ -4548,52 +4554,134 @@
       </c>
       <c r="O90" s="7"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A91" s="4"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="6"/>
-      <c r="M91" s="9">
+    <row r="91" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A91" s="2"/>
+      <c r="B91" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D91" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E91" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I91" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K91" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="L91" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="M91" s="10"/>
+      <c r="N91" s="10">
+        <v>1</v>
+      </c>
+      <c r="O91" s="7"/>
+    </row>
+    <row r="92" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A92" s="2"/>
+      <c r="B92" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E92" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I92" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K92" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="L92" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="M92" s="10"/>
+      <c r="N92" s="10">
+        <v>1</v>
+      </c>
+      <c r="O92" s="7"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A93" s="4"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="9">
         <v>0</v>
       </c>
-      <c r="N91" s="9">
-        <v>182</v>
-      </c>
-      <c r="O91" s="9">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A92" s="4"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="9">
-        <v>85</v>
-      </c>
-      <c r="I92" s="6"/>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6"/>
-      <c r="L92" s="6"/>
-      <c r="M92" s="9">
+      <c r="N93" s="9">
+        <v>189</v>
+      </c>
+      <c r="O93" s="9">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A94" s="4"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="9">
+        <v>87</v>
+      </c>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="9">
         <v>0</v>
       </c>
-      <c r="N92" s="9">
-        <v>394</v>
-      </c>
-      <c r="O92" s="9">
-        <v>85</v>
+      <c r="N94" s="9">
+        <v>401</v>
+      </c>
+      <c r="O94" s="9">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD2107F8-81A5-4303-A254-36AF54E01960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7B0AA9F-BDD3-4DB8-AEBB-E50A9FEA6FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{8EC2283C-B3A0-459D-A031-B95FA7985C31}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{4F01A82A-6053-40A1-B740-48809F7DEDF6}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="118">
   <si>
     <t>Dados</t>
   </si>
@@ -112,6 +112,9 @@
     <t>16/02/2026</t>
   </si>
   <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
     <t>22/01/2026</t>
   </si>
   <si>
@@ -283,13 +286,13 @@
     <t xml:space="preserve">CI003141-EM-CASA-961 - COPO CAFÉ FACETADO C/ IMPRESSÃO DIGITAL </t>
   </si>
   <si>
+    <t xml:space="preserve">CI003141-EM-CASA-1388 - COPO CAFÉ FACETADO C/ IMPRESSÃO DIGITAL </t>
+  </si>
+  <si>
     <t>CIPF002816STITCHCAP2624 - CORPO GARRAFA FUN 600 ML - STITCH CAPIVA</t>
   </si>
   <si>
     <t>CIPF002816-PRINCESAS-24 - CORPO GARRAFA FUN 600 ML - PRINCESAS 202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI003141-EM-CASA-1388 - COPO CAFÉ FACETADO C/ IMPRESSÃO DIGITAL </t>
   </si>
   <si>
     <t xml:space="preserve">CI002027-ARIEL_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - ARIEL </t>
@@ -915,8 +918,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987863C2-E270-4F1A-9430-C8823FDC7009}">
-  <dimension ref="A1:O94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E902DF-2118-4D25-BEFA-B7AF8A662001}">
+  <dimension ref="A1:O99"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -947,14 +950,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -968,40 +971,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1040,25 +1043,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1081,25 +1084,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1122,25 +1125,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1163,25 +1166,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1204,25 +1207,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1245,25 +1248,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1286,25 +1289,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1327,25 +1330,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1368,25 +1371,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1409,25 +1412,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1450,25 +1453,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1491,25 +1494,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1532,25 +1535,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1573,25 +1576,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1614,25 +1617,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1655,25 +1658,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1696,25 +1699,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1737,25 +1740,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1778,25 +1781,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1819,25 +1822,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1860,25 +1863,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1901,25 +1904,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1942,25 +1945,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -1983,25 +1986,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2024,25 +2027,25 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2065,25 +2068,25 @@
         <v>46027.4840625</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I29" s="7">
         <v>1404289</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2106,25 +2109,25 @@
         <v>46030.397997685184</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I30" s="7">
         <v>1394724</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2147,25 +2150,25 @@
         <v>46030.408148148148</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I31" s="7">
         <v>1394724</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2188,25 +2191,25 @@
         <v>46030.478854166664</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I32" s="7">
         <v>1394724</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2229,25 +2232,25 @@
         <v>46030.561284722222</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2270,25 +2273,25 @@
         <v>46035.478368055556</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2311,25 +2314,25 @@
         <v>46043.385474537034</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2352,25 +2355,25 @@
         <v>46043.565196759257</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2393,25 +2396,25 @@
         <v>46069.559953703705</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I37" s="7">
         <v>1421099</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
@@ -2434,25 +2437,25 @@
         <v>46078.552407407406</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I38" s="7">
         <v>1422286</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
@@ -2463,82 +2466,82 @@
     <row r="39" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D39" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="E39" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I39" s="7">
-        <v>1404958</v>
+        <v>1422285</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39" s="7"/>
     </row>
     <row r="40" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D40" s="8">
-        <v>46043.385196759256</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="E40" s="8">
-        <v>46043.385196759256</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I40" s="7">
-        <v>1405794</v>
+        <v>1422285</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>88</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O40" s="7"/>
     </row>
@@ -2548,38 +2551,38 @@
         <v>7</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D41" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E41" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>52</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>70</v>
       </c>
       <c r="I41" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O41" s="7"/>
     </row>
@@ -2592,35 +2595,35 @@
         <v>28</v>
       </c>
       <c r="D42" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E42" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I42" s="7">
         <v>1405794</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O42" s="7"/>
     </row>
@@ -2630,34 +2633,34 @@
         <v>7</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D43" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E43" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I43" s="7">
         <v>1405794</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
@@ -2671,38 +2674,38 @@
         <v>7</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D44" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E44" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>50</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I44" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O44" s="7"/>
     </row>
@@ -2712,38 +2715,38 @@
         <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D45" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E45" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I45" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O45" s="7"/>
     </row>
@@ -2753,38 +2756,38 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D46" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E46" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I46" s="7">
-        <v>1410338</v>
+        <v>1411351</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O46" s="7"/>
     </row>
@@ -2794,38 +2797,38 @@
         <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D47" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E47" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I47" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O47" s="7"/>
     </row>
@@ -2835,38 +2838,38 @@
         <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D48" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E48" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I48" s="7">
-        <v>1412987</v>
+        <v>1410338</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O48" s="7"/>
     </row>
@@ -2876,38 +2879,38 @@
         <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D49" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E49" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I49" s="7">
-        <v>1421099</v>
+        <v>1412987</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O49" s="7"/>
     </row>
@@ -2917,34 +2920,34 @@
         <v>7</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D50" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E50" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I50" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
@@ -2958,166 +2961,166 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D51" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="E51" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I51" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
+        <v>2</v>
+      </c>
+      <c r="O51" s="7"/>
+    </row>
+    <row r="52" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A52" s="2"/>
+      <c r="B52" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="E52" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I52" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10">
         <v>3</v>
       </c>
-      <c r="O51" s="7"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A52" s="4"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="9">
+      <c r="O52" s="7"/>
+    </row>
+    <row r="53" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A53" s="2"/>
+      <c r="B53" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="E53" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I53" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10">
+        <v>3</v>
+      </c>
+      <c r="O53" s="7"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A54" s="4"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="9">
         <v>0</v>
       </c>
-      <c r="N52" s="9">
-        <v>212</v>
-      </c>
-      <c r="O52" s="9">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
+      <c r="N54" s="9">
+        <v>227</v>
+      </c>
+      <c r="O54" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B55" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="12"/>
-      <c r="M53" s="12"/>
-      <c r="N53" s="12"/>
-      <c r="O53" s="12"/>
-    </row>
-    <row r="54" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A54" s="2"/>
-      <c r="B54" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D54" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="E54" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I54" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K54" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="L54" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10">
-        <v>3</v>
-      </c>
-      <c r="O54" s="7"/>
-    </row>
-    <row r="55" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A55" s="2"/>
-      <c r="B55" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D55" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E55" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I55" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="L55" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10">
-        <v>1</v>
-      </c>
-      <c r="O55" s="7"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12"/>
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
+      <c r="N55" s="12"/>
+      <c r="O55" s="12"/>
     </row>
     <row r="56" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
@@ -3125,38 +3128,38 @@
         <v>4</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D56" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E56" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I56" s="7">
-        <v>1406206</v>
+        <v>1386388</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O56" s="7"/>
     </row>
@@ -3166,38 +3169,38 @@
         <v>4</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D57" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E57" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I57" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O57" s="7"/>
     </row>
@@ -3207,38 +3210,38 @@
         <v>4</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D58" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E58" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I58" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O58" s="7"/>
     </row>
@@ -3251,35 +3254,35 @@
         <v>34</v>
       </c>
       <c r="D59" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E59" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I59" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O59" s="7"/>
     </row>
@@ -3289,38 +3292,38 @@
         <v>4</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D60" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E60" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I60" s="7">
         <v>1411990</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60" s="7"/>
     </row>
@@ -3333,31 +3336,31 @@
         <v>35</v>
       </c>
       <c r="D61" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E61" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>58</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I61" s="7">
         <v>1411990</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
@@ -3374,117 +3377,117 @@
         <v>36</v>
       </c>
       <c r="D62" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E62" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I62" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O62" s="7"/>
     </row>
     <row r="63" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D63" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E63" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I63" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O63" s="7"/>
     </row>
     <row r="64" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D64" s="8">
-        <v>46029.6719212963</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E64" s="8">
-        <v>46029.6719212963</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I64" s="7">
-        <v>1394721</v>
+        <v>1410767</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O64" s="7"/>
     </row>
@@ -3494,38 +3497,38 @@
         <v>5</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D65" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E65" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I65" s="7">
         <v>1394721</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O65" s="7"/>
     </row>
@@ -3535,38 +3538,38 @@
         <v>5</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D66" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E66" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>59</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I66" s="7">
         <v>1394721</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O66" s="7"/>
     </row>
@@ -3576,38 +3579,38 @@
         <v>5</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D67" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E67" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I67" s="7">
         <v>1394721</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O67" s="7"/>
     </row>
@@ -3617,38 +3620,38 @@
         <v>5</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D68" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E68" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I68" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3661,35 +3664,35 @@
         <v>41</v>
       </c>
       <c r="D69" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E69" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I69" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>79</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" s="7"/>
     </row>
@@ -3699,38 +3702,38 @@
         <v>5</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D70" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E70" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I70" s="7">
-        <v>1411708</v>
+        <v>1410339</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>95</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3743,35 +3746,35 @@
         <v>42</v>
       </c>
       <c r="D71" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E71" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I71" s="7">
-        <v>1418251</v>
+        <v>1411706</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3781,38 +3784,38 @@
         <v>5</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D72" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E72" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>58</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I72" s="7">
-        <v>1422511</v>
+        <v>1411708</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O72" s="7"/>
     </row>
@@ -3822,38 +3825,38 @@
         <v>5</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D73" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E73" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I73" s="7">
-        <v>1422511</v>
+        <v>1418251</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3863,120 +3866,120 @@
         <v>5</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D74" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E74" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>59</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I74" s="7">
         <v>1422511</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D75" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E75" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I75" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O75" s="7"/>
     </row>
     <row r="76" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D76" s="8">
-        <v>46029.802372685182</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E76" s="8">
-        <v>46029.802372685182</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I76" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -3986,38 +3989,38 @@
         <v>6</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D77" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E77" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>70</v>
       </c>
       <c r="I77" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>84</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O77" s="7"/>
     </row>
@@ -4027,19 +4030,19 @@
         <v>6</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D78" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E78" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H78" s="5" t="s">
         <v>70</v>
@@ -4048,17 +4051,17 @@
         <v>1394724</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O78" s="7"/>
     </row>
@@ -4068,38 +4071,38 @@
         <v>6</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D79" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E79" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I79" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4109,34 +4112,34 @@
         <v>6</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D80" s="8">
-        <v>46078.867326388892</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E80" s="8">
-        <v>46078.867326388892</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I80" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
@@ -4147,205 +4150,205 @@
     <row r="81" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>44</v>
       </c>
       <c r="D81" s="8">
-        <v>46024.795127314814</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E81" s="8">
-        <v>46024.795127314814</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>70</v>
       </c>
       <c r="I81" s="7">
-        <v>1398335</v>
+        <v>1422286</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O81" s="7"/>
     </row>
     <row r="82" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D82" s="8">
-        <v>46024.795277777775</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E82" s="8">
-        <v>46024.795277777775</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I82" s="7">
-        <v>1398335</v>
+        <v>1422286</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O82" s="7"/>
     </row>
     <row r="83" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D83" s="8">
-        <v>46024.900324074071</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E83" s="8">
-        <v>46024.900324074071</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>70</v>
       </c>
       <c r="I83" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O83" s="7"/>
     </row>
     <row r="84" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D84" s="8">
-        <v>46028.866898148146</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E84" s="8">
-        <v>46028.866898148146</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>70</v>
       </c>
       <c r="I84" s="7">
-        <v>1402956</v>
+        <v>1422285</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O84" s="7"/>
     </row>
     <row r="85" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D85" s="8">
-        <v>46034.751261574071</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E85" s="8">
-        <v>46034.751261574071</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I85" s="7">
-        <v>1404958</v>
+        <v>1422285</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4355,38 +4358,38 @@
         <v>7</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D86" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E86" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I86" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O86" s="7"/>
     </row>
@@ -4399,35 +4402,35 @@
         <v>45</v>
       </c>
       <c r="D87" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E87" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I87" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O87" s="7"/>
     </row>
@@ -4437,38 +4440,38 @@
         <v>7</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D88" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E88" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I88" s="7">
-        <v>1411991</v>
+        <v>1398335</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>98</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O88" s="7"/>
     </row>
@@ -4478,38 +4481,38 @@
         <v>7</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D89" s="8">
-        <v>46069.700543981482</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E89" s="8">
-        <v>46069.700543981482</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I89" s="7">
-        <v>1411991</v>
+        <v>1402956</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O89" s="7"/>
     </row>
@@ -4519,38 +4522,38 @@
         <v>7</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D90" s="8">
-        <v>46077.65824074074</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E90" s="8">
-        <v>46077.65824074074</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I90" s="7">
-        <v>1422285</v>
+        <v>1404958</v>
       </c>
       <c r="J90" s="5" t="s">
         <v>89</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O90" s="7"/>
     </row>
@@ -4560,34 +4563,34 @@
         <v>7</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D91" s="8">
-        <v>46078.881018518521</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E91" s="8">
-        <v>46078.881018518521</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I91" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
@@ -4601,87 +4604,292 @@
         <v>7</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D92" s="8">
-        <v>46079.901782407411</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E92" s="8">
-        <v>46079.901782407411</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I92" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
+        <v>5</v>
+      </c>
+      <c r="O92" s="7"/>
+    </row>
+    <row r="93" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A93" s="2"/>
+      <c r="B93" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E93" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I93" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K93" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L93" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M93" s="10"/>
+      <c r="N93" s="10">
+        <v>3</v>
+      </c>
+      <c r="O93" s="7"/>
+    </row>
+    <row r="94" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A94" s="2"/>
+      <c r="B94" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E94" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I94" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="K94" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L94" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M94" s="10"/>
+      <c r="N94" s="10">
+        <v>10</v>
+      </c>
+      <c r="O94" s="7"/>
+    </row>
+    <row r="95" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A95" s="2"/>
+      <c r="B95" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E95" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I95" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K95" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L95" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="M95" s="10"/>
+      <c r="N95" s="10">
         <v>1</v>
       </c>
-      <c r="O92" s="7"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A93" s="4"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
-      <c r="M93" s="9">
+      <c r="O95" s="7"/>
+    </row>
+    <row r="96" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A96" s="2"/>
+      <c r="B96" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E96" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I96" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K96" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L96" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M96" s="10"/>
+      <c r="N96" s="10">
+        <v>1</v>
+      </c>
+      <c r="O96" s="7"/>
+    </row>
+    <row r="97" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A97" s="2"/>
+      <c r="B97" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D97" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E97" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I97" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K97" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L97" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="M97" s="10"/>
+      <c r="N97" s="10">
+        <v>1</v>
+      </c>
+      <c r="O97" s="7"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A98" s="4"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="9">
         <v>0</v>
       </c>
-      <c r="N93" s="9">
-        <v>189</v>
-      </c>
-      <c r="O93" s="9">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A94" s="4"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="9">
-        <v>87</v>
-      </c>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="9">
+      <c r="N98" s="9">
+        <v>193</v>
+      </c>
+      <c r="O98" s="9">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A99" s="4"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="9">
+        <v>92</v>
+      </c>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="9">
         <v>0</v>
       </c>
-      <c r="N94" s="9">
-        <v>401</v>
-      </c>
-      <c r="O94" s="9">
-        <v>87</v>
+      <c r="N99" s="9">
+        <v>420</v>
+      </c>
+      <c r="O99" s="9">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4691,7 +4899,7 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B53:O53"/>
+    <mergeCell ref="B55:O55"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7B0AA9F-BDD3-4DB8-AEBB-E50A9FEA6FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19DC66B3-3CD7-47B7-A5E3-4F7F8A2BFCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{4F01A82A-6053-40A1-B740-48809F7DEDF6}"/>
+    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{4ECDC1E8-0168-42FA-AC67-97447CB55B84}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="121">
   <si>
     <t>Dados</t>
   </si>
@@ -103,6 +103,9 @@
     <t>25/02/2026</t>
   </si>
   <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
     <t>05/01/2026</t>
   </si>
   <si>
@@ -157,6 +160,9 @@
     <t>23/02/2026</t>
   </si>
   <si>
+    <t>28/02/2026</t>
+  </si>
+  <si>
     <t>02/01/2026</t>
   </si>
   <si>
@@ -272,6 +278,9 @@
   </si>
   <si>
     <t>CI002027-CINDERELA_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - CINDER</t>
+  </si>
+  <si>
+    <t>CI002027-BELA_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - BELA 2</t>
   </si>
   <si>
     <t>CIPF002816-TOYSTORY_26-24 - CORPO GARRAFA FUN 600 ML - TOY&amp;STORY 202</t>
@@ -380,7 +389,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -397,6 +406,15 @@
       <sz val="8"/>
       <color indexed="61"/>
       <name val="MS Sans Serif"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color indexed="61"/>
+      <name val="Small Fonts"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Small Fonts"/>
     </font>
   </fonts>
   <fills count="4">
@@ -479,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -508,7 +526,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -918,8 +939,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E902DF-2118-4D25-BEFA-B7AF8A662001}">
-  <dimension ref="A1:O99"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7871C00D-FAC7-48AD-8BF9-149DAB71ED81}">
+  <dimension ref="A1:O103"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -940,93 +961,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
+      <c r="B2" s="12"/>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -1043,29 +1064,29 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
-        <v>1</v>
+        <v>44.2</v>
       </c>
       <c r="O4" s="7"/>
     </row>
@@ -1084,29 +1105,29 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
-        <v>2</v>
+        <v>88.4</v>
       </c>
       <c r="O5" s="7"/>
     </row>
@@ -1125,29 +1146,29 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
-        <v>5</v>
+        <v>261.11500000000001</v>
       </c>
       <c r="O6" s="7"/>
     </row>
@@ -1166,29 +1187,29 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
-        <v>5</v>
+        <v>261.63</v>
       </c>
       <c r="O7" s="7"/>
     </row>
@@ -1207,29 +1228,29 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
-        <v>2</v>
+        <v>54.2</v>
       </c>
       <c r="O8" s="7"/>
     </row>
@@ -1248,29 +1269,29 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
-        <v>8</v>
+        <v>418.608</v>
       </c>
       <c r="O9" s="7"/>
     </row>
@@ -1289,29 +1310,29 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
-        <v>6</v>
+        <v>313.95600000000002</v>
       </c>
       <c r="O10" s="7"/>
     </row>
@@ -1330,29 +1351,29 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
-        <v>12</v>
+        <v>627.91200000000003</v>
       </c>
       <c r="O11" s="7"/>
     </row>
@@ -1371,29 +1392,29 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
-        <v>5</v>
+        <v>261.11500000000001</v>
       </c>
       <c r="O12" s="7"/>
     </row>
@@ -1412,29 +1433,29 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
-        <v>5</v>
+        <v>225.5</v>
       </c>
       <c r="O13" s="7"/>
     </row>
@@ -1453,29 +1474,29 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
-        <v>1</v>
+        <v>44.2</v>
       </c>
       <c r="O14" s="7"/>
     </row>
@@ -1494,29 +1515,29 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
-        <v>9</v>
+        <v>397.8</v>
       </c>
       <c r="O15" s="7"/>
     </row>
@@ -1535,29 +1556,29 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
-        <v>3</v>
+        <v>132.60000000000002</v>
       </c>
       <c r="O16" s="7"/>
     </row>
@@ -1576,29 +1597,29 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
-        <v>1</v>
+        <v>45.1</v>
       </c>
       <c r="O17" s="7"/>
     </row>
@@ -1617,29 +1638,29 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
-        <v>1</v>
+        <v>45.1</v>
       </c>
       <c r="O18" s="7"/>
     </row>
@@ -1658,29 +1679,29 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
-        <v>2</v>
+        <v>90.2</v>
       </c>
       <c r="O19" s="7"/>
     </row>
@@ -1699,29 +1720,29 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
-        <v>3</v>
+        <v>135.30000000000001</v>
       </c>
       <c r="O20" s="7"/>
     </row>
@@ -1740,29 +1761,29 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
-        <v>4</v>
+        <v>180.33600000000001</v>
       </c>
       <c r="O21" s="7"/>
     </row>
@@ -1781,29 +1802,29 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
-        <v>4</v>
+        <v>180.4</v>
       </c>
       <c r="O22" s="7"/>
     </row>
@@ -1822,29 +1843,29 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
-        <v>3</v>
+        <v>135.30000000000001</v>
       </c>
       <c r="O23" s="7"/>
     </row>
@@ -1863,29 +1884,29 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
-        <v>2</v>
+        <v>90.2</v>
       </c>
       <c r="O24" s="7"/>
     </row>
@@ -1904,29 +1925,29 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
-        <v>4</v>
+        <v>176.8</v>
       </c>
       <c r="O25" s="7"/>
     </row>
@@ -1945,29 +1966,29 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
-        <v>21</v>
+        <v>947.1</v>
       </c>
       <c r="O26" s="7"/>
     </row>
@@ -1986,29 +2007,29 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
-        <v>2</v>
+        <v>90.2</v>
       </c>
       <c r="O27" s="7"/>
     </row>
@@ -2027,70 +2048,70 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
-        <v>4</v>
+        <v>180.4</v>
       </c>
       <c r="O28" s="7"/>
     </row>
     <row r="29" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D29" s="8">
-        <v>46027.4840625</v>
+        <v>46083.272581018522</v>
       </c>
       <c r="E29" s="8">
-        <v>46027.4840625</v>
+        <v>46083.272581018522</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I29" s="7">
-        <v>1404289</v>
+        <v>1423124</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
-        <v>3</v>
+        <v>45.1</v>
       </c>
       <c r="O29" s="7"/>
     </row>
@@ -2100,38 +2121,38 @@
         <v>6</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D30" s="8">
-        <v>46030.397997685184</v>
+        <v>46027.4840625</v>
       </c>
       <c r="E30" s="8">
-        <v>46030.397997685184</v>
+        <v>46027.4840625</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I30" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
-        <v>4</v>
+        <v>264.02699999999999</v>
       </c>
       <c r="O30" s="7"/>
     </row>
@@ -2144,35 +2165,35 @@
         <v>17</v>
       </c>
       <c r="D31" s="8">
-        <v>46030.408148148148</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="E31" s="8">
-        <v>46030.408148148148</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I31" s="7">
         <v>1394724</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
-        <v>4</v>
+        <v>352.036</v>
       </c>
       <c r="O31" s="7"/>
     </row>
@@ -2185,35 +2206,35 @@
         <v>17</v>
       </c>
       <c r="D32" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="E32" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I32" s="7">
         <v>1394724</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
-        <v>4</v>
+        <v>352.036</v>
       </c>
       <c r="O32" s="7"/>
     </row>
@@ -2226,35 +2247,35 @@
         <v>17</v>
       </c>
       <c r="D33" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="E33" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
-        <v>2</v>
+        <v>352.036</v>
       </c>
       <c r="O33" s="7"/>
     </row>
@@ -2264,38 +2285,38 @@
         <v>6</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D34" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="E34" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
-        <v>6</v>
+        <v>176.018</v>
       </c>
       <c r="O34" s="7"/>
     </row>
@@ -2305,38 +2326,38 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D35" s="8">
-        <v>46043.385474537034</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="E35" s="8">
-        <v>46043.385474537034</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
-        <v>3</v>
+        <v>528.05399999999997</v>
       </c>
       <c r="O35" s="7"/>
     </row>
@@ -2346,38 +2367,38 @@
         <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" s="8">
-        <v>46043.565196759257</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="E36" s="8">
-        <v>46043.565196759257</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
-        <v>3</v>
+        <v>264.02699999999999</v>
       </c>
       <c r="O36" s="7"/>
     </row>
@@ -2390,35 +2411,35 @@
         <v>29</v>
       </c>
       <c r="D37" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="E37" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I37" s="7">
-        <v>1421099</v>
+        <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
-        <v>5</v>
+        <v>264.02699999999999</v>
       </c>
       <c r="O37" s="7"/>
     </row>
@@ -2428,38 +2449,38 @@
         <v>6</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D38" s="8">
-        <v>46078.552407407406</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="E38" s="8">
-        <v>46078.552407407406</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I38" s="7">
-        <v>1422286</v>
+        <v>1421099</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
-        <v>5</v>
+        <v>221</v>
       </c>
       <c r="O38" s="7"/>
     </row>
@@ -2469,38 +2490,38 @@
         <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D39" s="8">
-        <v>46080.522418981483</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="E39" s="8">
-        <v>46080.522418981483</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I39" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>6</v>
+        <v>261.11500000000001</v>
       </c>
       <c r="O39" s="7"/>
     </row>
@@ -2510,120 +2531,120 @@
         <v>6</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D40" s="8">
-        <v>46080.532164351855</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="E40" s="8">
-        <v>46080.532164351855</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I40" s="7">
         <v>1422285</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>9</v>
+        <v>313.33799999999997</v>
       </c>
       <c r="O40" s="7"/>
     </row>
     <row r="41" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D41" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="E41" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I41" s="7">
-        <v>1404958</v>
+        <v>1422285</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <v>3</v>
+        <v>470.00700000000001</v>
       </c>
       <c r="O41" s="7"/>
     </row>
     <row r="42" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D42" s="8">
-        <v>46043.385196759256</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="E42" s="8">
-        <v>46043.385196759256</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I42" s="7">
-        <v>1405794</v>
+        <v>1422283</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>4</v>
+        <v>156.66899999999998</v>
       </c>
       <c r="O42" s="7"/>
     </row>
@@ -2633,38 +2654,38 @@
         <v>7</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D43" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E43" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I43" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <v>2</v>
+        <v>264.02699999999999</v>
       </c>
       <c r="O43" s="7"/>
     </row>
@@ -2674,38 +2695,38 @@
         <v>7</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D44" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E44" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I44" s="7">
         <v>1405794</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>3</v>
+        <v>352.036</v>
       </c>
       <c r="O44" s="7"/>
     </row>
@@ -2715,38 +2736,38 @@
         <v>7</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D45" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E45" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I45" s="7">
         <v>1405794</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <v>2</v>
+        <v>176.018</v>
       </c>
       <c r="O45" s="7"/>
     </row>
@@ -2756,38 +2777,38 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D46" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E46" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I46" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
-        <v>12</v>
+        <v>264.02699999999999</v>
       </c>
       <c r="O46" s="7"/>
     </row>
@@ -2797,38 +2818,38 @@
         <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D47" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E47" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I47" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <v>5</v>
+        <v>176.018</v>
       </c>
       <c r="O47" s="7"/>
     </row>
@@ -2838,38 +2859,38 @@
         <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D48" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E48" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I48" s="7">
-        <v>1410338</v>
+        <v>1411351</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
-        <v>10</v>
+        <v>626.67599999999993</v>
       </c>
       <c r="O48" s="7"/>
     </row>
@@ -2879,38 +2900,38 @@
         <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D49" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E49" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I49" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <v>6</v>
+        <v>261.11500000000001</v>
       </c>
       <c r="O49" s="7"/>
     </row>
@@ -2920,38 +2941,38 @@
         <v>7</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D50" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E50" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I50" s="7">
-        <v>1412987</v>
+        <v>1410338</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
-        <v>3</v>
+        <v>451</v>
       </c>
       <c r="O50" s="7"/>
     </row>
@@ -2961,38 +2982,38 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D51" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E51" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I51" s="7">
-        <v>1421099</v>
+        <v>1412987</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
-        <v>2</v>
+        <v>265.20000000000005</v>
       </c>
       <c r="O51" s="7"/>
     </row>
@@ -3002,38 +3023,38 @@
         <v>7</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D52" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E52" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I52" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <v>3</v>
+        <v>132.60000000000002</v>
       </c>
       <c r="O52" s="7"/>
     </row>
@@ -3043,166 +3064,166 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="E53" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I53" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
-        <v>3</v>
+        <v>88.4</v>
       </c>
       <c r="O53" s="7"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A54" s="4"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="9">
+    <row r="54" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A54" s="2"/>
+      <c r="B54" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="E54" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I54" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10">
+        <v>156.66899999999998</v>
+      </c>
+      <c r="O54" s="7"/>
+    </row>
+    <row r="55" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A55" s="2"/>
+      <c r="B55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="E55" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I55" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10">
+        <v>156.66899999999998</v>
+      </c>
+      <c r="O55" s="7"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" s="4"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="11">
         <v>0</v>
       </c>
-      <c r="N54" s="9">
-        <v>227</v>
-      </c>
-      <c r="O54" s="9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
+      <c r="N56" s="11">
+        <v>12817.616999999998</v>
+      </c>
+      <c r="O56" s="9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
-      <c r="L55" s="12"/>
-      <c r="M55" s="12"/>
-      <c r="N55" s="12"/>
-      <c r="O55" s="12"/>
-    </row>
-    <row r="56" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A56" s="2"/>
-      <c r="B56" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D56" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="E56" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I56" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L56" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10">
-        <v>3</v>
-      </c>
-      <c r="O56" s="7"/>
-    </row>
-    <row r="57" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A57" s="2"/>
-      <c r="B57" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D57" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E57" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H57" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I57" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="L57" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10">
-        <v>1</v>
-      </c>
-      <c r="O57" s="7"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
     </row>
     <row r="58" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
@@ -3210,38 +3231,38 @@
         <v>4</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D58" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E58" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I58" s="7">
-        <v>1406206</v>
+        <v>1386388</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>11</v>
+        <v>132.60000000000002</v>
       </c>
       <c r="O58" s="7"/>
     </row>
@@ -3251,38 +3272,38 @@
         <v>4</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D59" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E59" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I59" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>76</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>9</v>
+        <v>44.2</v>
       </c>
       <c r="O59" s="7"/>
     </row>
@@ -3292,38 +3313,38 @@
         <v>4</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D60" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E60" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I60" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
-        <v>2</v>
+        <v>977.84499999999991</v>
       </c>
       <c r="O60" s="7"/>
     </row>
@@ -3336,35 +3357,35 @@
         <v>35</v>
       </c>
       <c r="D61" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E61" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I61" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
-        <v>2</v>
+        <v>470.93400000000003</v>
       </c>
       <c r="O61" s="7"/>
     </row>
@@ -3374,38 +3395,38 @@
         <v>4</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D62" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E62" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I62" s="7">
         <v>1411990</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>1</v>
+        <v>104.446</v>
       </c>
       <c r="O62" s="7"/>
     </row>
@@ -3418,35 +3439,35 @@
         <v>36</v>
       </c>
       <c r="D63" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E63" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I63" s="7">
         <v>1411990</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
-        <v>2</v>
+        <v>104.446</v>
       </c>
       <c r="O63" s="7"/>
     </row>
@@ -3459,117 +3480,117 @@
         <v>37</v>
       </c>
       <c r="D64" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E64" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I64" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>6</v>
+        <v>52.222999999999999</v>
       </c>
       <c r="O64" s="7"/>
     </row>
     <row r="65" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D65" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E65" s="8">
-        <v>46028.907905092594</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I65" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>15</v>
+        <v>104.446</v>
       </c>
       <c r="O65" s="7"/>
     </row>
     <row r="66" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>38</v>
       </c>
       <c r="D66" s="8">
-        <v>46029.6719212963</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E66" s="8">
-        <v>46029.6719212963</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I66" s="7">
-        <v>1394721</v>
+        <v>1410767</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>4</v>
+        <v>160.19999999999999</v>
       </c>
       <c r="O66" s="7"/>
     </row>
@@ -3579,38 +3600,38 @@
         <v>5</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D67" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E67" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>63</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I67" s="7">
         <v>1394721</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>3</v>
+        <v>663</v>
       </c>
       <c r="O67" s="7"/>
     </row>
@@ -3620,38 +3641,38 @@
         <v>5</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D68" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E68" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I68" s="7">
         <v>1394721</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>14</v>
+        <v>176.8</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3661,38 +3682,38 @@
         <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D69" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E69" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I69" s="7">
         <v>1394721</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>1</v>
+        <v>132.60000000000002</v>
       </c>
       <c r="O69" s="7"/>
     </row>
@@ -3702,38 +3723,38 @@
         <v>5</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D70" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E70" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I70" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>1</v>
+        <v>618.80000000000007</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3746,35 +3767,35 @@
         <v>42</v>
       </c>
       <c r="D71" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E71" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I71" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L71" s="7" t="s">
         <v>109</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>2</v>
+        <v>44.2</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3784,38 +3805,38 @@
         <v>5</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D72" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E72" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I72" s="7">
-        <v>1411708</v>
+        <v>1410339</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L72" s="7" t="s">
         <v>109</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>9</v>
+        <v>45.1</v>
       </c>
       <c r="O72" s="7"/>
     </row>
@@ -3828,35 +3849,35 @@
         <v>43</v>
       </c>
       <c r="D73" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E73" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I73" s="7">
-        <v>1418251</v>
+        <v>1411706</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>1</v>
+        <v>90.168000000000006</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3866,38 +3887,38 @@
         <v>5</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D74" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E74" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I74" s="7">
-        <v>1422511</v>
+        <v>1411708</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>1</v>
+        <v>405.75600000000003</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3907,38 +3928,38 @@
         <v>5</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D75" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E75" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I75" s="7">
-        <v>1422511</v>
+        <v>1418251</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>4</v>
+        <v>77.8</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3948,107 +3969,107 @@
         <v>5</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D76" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E76" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I76" s="7">
         <v>1422511</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>12</v>
+        <v>45.1</v>
       </c>
       <c r="O76" s="7"/>
     </row>
     <row r="77" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D77" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E77" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I77" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K77" s="5" t="s">
         <v>104</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>3</v>
+        <v>180.4</v>
       </c>
       <c r="O77" s="7"/>
     </row>
     <row r="78" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D78" s="8">
-        <v>46029.802372685182</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E78" s="8">
-        <v>46029.802372685182</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I78" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>85</v>
@@ -4057,11 +4078,11 @@
         <v>104</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>10</v>
+        <v>541.20000000000005</v>
       </c>
       <c r="O78" s="7"/>
     </row>
@@ -4071,38 +4092,38 @@
         <v>6</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D79" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E79" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I79" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>5</v>
+        <v>264.02699999999999</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4112,38 +4133,38 @@
         <v>6</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D80" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E80" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I80" s="7">
         <v>1394724</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>4</v>
+        <v>880.09</v>
       </c>
       <c r="O80" s="7"/>
     </row>
@@ -4153,38 +4174,38 @@
         <v>6</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D81" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E81" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I81" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
-        <v>15</v>
+        <v>440.04500000000002</v>
       </c>
       <c r="O81" s="7"/>
     </row>
@@ -4194,38 +4215,38 @@
         <v>6</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D82" s="8">
-        <v>46078.867326388892</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E82" s="8">
-        <v>46078.867326388892</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I82" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>4</v>
+        <v>352.036</v>
       </c>
       <c r="O82" s="7"/>
     </row>
@@ -4235,38 +4256,38 @@
         <v>6</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D83" s="8">
-        <v>46080.639293981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E83" s="8">
-        <v>46080.639293981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I83" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>2</v>
+        <v>783.34500000000003</v>
       </c>
       <c r="O83" s="7"/>
     </row>
@@ -4276,38 +4297,38 @@
         <v>6</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D84" s="8">
-        <v>46080.716932870368</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E84" s="8">
-        <v>46080.716932870368</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I84" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>1</v>
+        <v>208.892</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4317,202 +4338,202 @@
         <v>6</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D85" s="8">
-        <v>46080.740543981483</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E85" s="8">
-        <v>46080.740543981483</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I85" s="7">
         <v>1422285</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>1</v>
+        <v>104.446</v>
       </c>
       <c r="O85" s="7"/>
     </row>
     <row r="86" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D86" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E86" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I86" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>6</v>
+        <v>52.222999999999999</v>
       </c>
       <c r="O86" s="7"/>
     </row>
     <row r="87" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D87" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E87" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I87" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>2</v>
+        <v>52.222999999999999</v>
       </c>
       <c r="O87" s="7"/>
     </row>
     <row r="88" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D88" s="8">
-        <v>46024.900324074071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E88" s="8">
-        <v>46024.900324074071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I88" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>5</v>
+        <v>52.222999999999999</v>
       </c>
       <c r="O88" s="7"/>
     </row>
     <row r="89" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D89" s="8">
-        <v>46028.866898148146</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E89" s="8">
-        <v>46028.866898148146</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I89" s="7">
-        <v>1402956</v>
+        <v>1422283</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>2</v>
+        <v>2350.0349999999999</v>
       </c>
       <c r="O89" s="7"/>
     </row>
@@ -4522,38 +4543,38 @@
         <v>7</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D90" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E90" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I90" s="7">
-        <v>1404958</v>
+        <v>1398335</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>7</v>
+        <v>265.20000000000005</v>
       </c>
       <c r="O90" s="7"/>
     </row>
@@ -4563,38 +4584,38 @@
         <v>7</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="D91" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E91" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I91" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>1</v>
+        <v>88.4</v>
       </c>
       <c r="O91" s="7"/>
     </row>
@@ -4604,38 +4625,38 @@
         <v>7</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D92" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E92" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I92" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>5</v>
+        <v>221</v>
       </c>
       <c r="O92" s="7"/>
     </row>
@@ -4645,38 +4666,38 @@
         <v>7</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D93" s="8">
-        <v>46067.906875000001</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E93" s="8">
-        <v>46067.906875000001</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I93" s="7">
-        <v>1411991</v>
+        <v>1402956</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>3</v>
+        <v>90.168000000000006</v>
       </c>
       <c r="O93" s="7"/>
     </row>
@@ -4686,38 +4707,38 @@
         <v>7</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D94" s="8">
-        <v>46069.700543981482</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E94" s="8">
-        <v>46069.700543981482</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I94" s="7">
-        <v>1411991</v>
+        <v>1404958</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>10</v>
+        <v>616.06299999999999</v>
       </c>
       <c r="O94" s="7"/>
     </row>
@@ -4727,38 +4748,38 @@
         <v>7</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D95" s="8">
-        <v>46077.65824074074</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E95" s="8">
-        <v>46077.65824074074</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I95" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>1</v>
+        <v>44.2</v>
       </c>
       <c r="O95" s="7"/>
     </row>
@@ -4768,38 +4789,38 @@
         <v>7</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D96" s="8">
-        <v>46078.881018518521</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E96" s="8">
-        <v>46078.881018518521</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I96" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>1</v>
+        <v>221</v>
       </c>
       <c r="O96" s="7"/>
     </row>
@@ -4809,87 +4830,251 @@
         <v>7</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D97" s="8">
-        <v>46079.901782407411</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="E97" s="8">
-        <v>46079.901782407411</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I97" s="7">
-        <v>1423123</v>
+        <v>1411991</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>1</v>
+        <v>156.66899999999998</v>
       </c>
       <c r="O97" s="7"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A98" s="4"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
-      <c r="M98" s="9">
+    <row r="98" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A98" s="2"/>
+      <c r="B98" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E98" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I98" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="K98" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="M98" s="10"/>
+      <c r="N98" s="10">
+        <v>522.23</v>
+      </c>
+      <c r="O98" s="7"/>
+    </row>
+    <row r="99" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A99" s="2"/>
+      <c r="B99" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E99" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I99" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K99" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="L99" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M99" s="10"/>
+      <c r="N99" s="10">
+        <v>52.222999999999999</v>
+      </c>
+      <c r="O99" s="7"/>
+    </row>
+    <row r="100" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A100" s="2"/>
+      <c r="B100" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D100" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E100" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I100" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K100" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="L100" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="M100" s="10"/>
+      <c r="N100" s="10">
+        <v>44.2</v>
+      </c>
+      <c r="O100" s="7"/>
+    </row>
+    <row r="101" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A101" s="2"/>
+      <c r="B101" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D101" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E101" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I101" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K101" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="L101" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="M101" s="10"/>
+      <c r="N101" s="10">
+        <v>44.2</v>
+      </c>
+      <c r="O101" s="7"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A102" s="4"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="11">
         <v>0</v>
       </c>
-      <c r="N98" s="9">
-        <v>193</v>
-      </c>
-      <c r="O98" s="9">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A99" s="4"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="9">
-        <v>92</v>
-      </c>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="9">
+      <c r="N102" s="11">
+        <v>13077.402000000002</v>
+      </c>
+      <c r="O102" s="9">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A103" s="4"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="9">
+        <v>96</v>
+      </c>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="11">
         <v>0</v>
       </c>
-      <c r="N99" s="9">
-        <v>420</v>
-      </c>
-      <c r="O99" s="9">
-        <v>92</v>
+      <c r="N103" s="11">
+        <v>25895.019000000018</v>
+      </c>
+      <c r="O103" s="9">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -4899,7 +5084,7 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B55:O55"/>
+    <mergeCell ref="B57:O57"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19DC66B3-3CD7-47B7-A5E3-4F7F8A2BFCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F858FCC-9CE8-4CA4-92C5-9A807034D2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="3930" windowWidth="21600" windowHeight="11295" xr2:uid="{4ECDC1E8-0168-42FA-AC67-97447CB55B84}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{463ADD43-9B69-45E4-B575-83E842D7E9F2}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="124">
   <si>
     <t>Dados</t>
   </si>
@@ -106,6 +106,9 @@
     <t>02/03/2026</t>
   </si>
   <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
     <t>05/01/2026</t>
   </si>
   <si>
@@ -139,6 +142,9 @@
     <t>26/02/2026</t>
   </si>
   <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
     <t>07/01/2026</t>
   </si>
   <si>
@@ -281,6 +287,9 @@
   </si>
   <si>
     <t>CI002027-BELA_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - BELA 2</t>
+  </si>
+  <si>
+    <t>CIPF002438-PRINCESAS-24 - GARRAFA ABRE FACIL530ML - IMPRESSAO DIGI</t>
   </si>
   <si>
     <t>CIPF002816-TOYSTORY_26-24 - CORPO GARRAFA FUN 600 ML - TOY&amp;STORY 202</t>
@@ -389,7 +398,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -406,15 +415,6 @@
       <sz val="8"/>
       <color indexed="61"/>
       <name val="MS Sans Serif"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color indexed="61"/>
-      <name val="Small Fonts"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <name val="Small Fonts"/>
     </font>
   </fonts>
   <fills count="4">
@@ -497,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -526,10 +526,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -939,8 +936,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7871C00D-FAC7-48AD-8BF9-149DAB71ED81}">
-  <dimension ref="A1:O103"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9BE098-F4B4-4F86-9F10-454FDC02BB27}">
+  <dimension ref="A1:O109"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -961,93 +958,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
+      <c r="B2" s="11"/>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
     </row>
     <row r="4" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -1064,29 +1061,29 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
-        <v>44.2</v>
+        <v>1</v>
       </c>
       <c r="O4" s="7"/>
     </row>
@@ -1105,29 +1102,29 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
-        <v>88.4</v>
+        <v>2</v>
       </c>
       <c r="O5" s="7"/>
     </row>
@@ -1146,29 +1143,29 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
-        <v>261.11500000000001</v>
+        <v>5</v>
       </c>
       <c r="O6" s="7"/>
     </row>
@@ -1187,29 +1184,29 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
-        <v>261.63</v>
+        <v>5</v>
       </c>
       <c r="O7" s="7"/>
     </row>
@@ -1228,29 +1225,29 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
-        <v>54.2</v>
+        <v>2</v>
       </c>
       <c r="O8" s="7"/>
     </row>
@@ -1269,29 +1266,29 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
-        <v>418.608</v>
+        <v>8</v>
       </c>
       <c r="O9" s="7"/>
     </row>
@@ -1310,29 +1307,29 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
-        <v>313.95600000000002</v>
+        <v>6</v>
       </c>
       <c r="O10" s="7"/>
     </row>
@@ -1351,29 +1348,29 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
-        <v>627.91200000000003</v>
+        <v>12</v>
       </c>
       <c r="O11" s="7"/>
     </row>
@@ -1392,29 +1389,29 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
-        <v>261.11500000000001</v>
+        <v>5</v>
       </c>
       <c r="O12" s="7"/>
     </row>
@@ -1433,29 +1430,29 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I13" s="7">
         <v>1402958</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
-        <v>225.5</v>
+        <v>5</v>
       </c>
       <c r="O13" s="7"/>
     </row>
@@ -1474,29 +1471,29 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I14" s="7">
         <v>1394721</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
-        <v>44.2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="7"/>
     </row>
@@ -1515,29 +1512,29 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
-        <v>397.8</v>
+        <v>9</v>
       </c>
       <c r="O15" s="7"/>
     </row>
@@ -1556,29 +1553,29 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
-        <v>132.60000000000002</v>
+        <v>3</v>
       </c>
       <c r="O16" s="7"/>
     </row>
@@ -1597,29 +1594,29 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I17" s="7">
         <v>1410340</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
-        <v>45.1</v>
+        <v>1</v>
       </c>
       <c r="O17" s="7"/>
     </row>
@@ -1638,29 +1635,29 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
-        <v>45.1</v>
+        <v>1</v>
       </c>
       <c r="O18" s="7"/>
     </row>
@@ -1679,29 +1676,29 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
-        <v>90.2</v>
+        <v>2</v>
       </c>
       <c r="O19" s="7"/>
     </row>
@@ -1720,29 +1717,29 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
-        <v>135.30000000000001</v>
+        <v>3</v>
       </c>
       <c r="O20" s="7"/>
     </row>
@@ -1761,29 +1758,29 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I21" s="7">
         <v>1411706</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
-        <v>180.33600000000001</v>
+        <v>4</v>
       </c>
       <c r="O21" s="7"/>
     </row>
@@ -1802,29 +1799,29 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I22" s="7">
         <v>1411704</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
-        <v>180.4</v>
+        <v>4</v>
       </c>
       <c r="O22" s="7"/>
     </row>
@@ -1843,29 +1840,29 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
-        <v>135.30000000000001</v>
+        <v>3</v>
       </c>
       <c r="O23" s="7"/>
     </row>
@@ -1884,29 +1881,29 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
-        <v>90.2</v>
+        <v>2</v>
       </c>
       <c r="O24" s="7"/>
     </row>
@@ -1925,29 +1922,29 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I25" s="7">
         <v>1418256</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
-        <v>176.8</v>
+        <v>4</v>
       </c>
       <c r="O25" s="7"/>
     </row>
@@ -1966,29 +1963,29 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I26" s="7">
         <v>1422511</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
-        <v>947.1</v>
+        <v>21</v>
       </c>
       <c r="O26" s="7"/>
     </row>
@@ -2007,29 +2004,29 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
-        <v>90.2</v>
+        <v>2</v>
       </c>
       <c r="O27" s="7"/>
     </row>
@@ -2048,29 +2045,29 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
-        <v>180.4</v>
+        <v>4</v>
       </c>
       <c r="O28" s="7"/>
     </row>
@@ -2089,111 +2086,111 @@
         <v>46083.272581018522</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I29" s="7">
         <v>1423124</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
-        <v>45.1</v>
+        <v>1</v>
       </c>
       <c r="O29" s="7"/>
     </row>
     <row r="30" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D30" s="8">
-        <v>46027.4840625</v>
+        <v>46085.323807870373</v>
       </c>
       <c r="E30" s="8">
-        <v>46027.4840625</v>
+        <v>46085.323807870373</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I30" s="7">
-        <v>1404289</v>
+        <v>1428373</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
-        <v>264.02699999999999</v>
+        <v>2</v>
       </c>
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D31" s="8">
-        <v>46030.397997685184</v>
+        <v>46085.344675925924</v>
       </c>
       <c r="E31" s="8">
-        <v>46030.397997685184</v>
+        <v>46085.344675925924</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I31" s="7">
-        <v>1394724</v>
+        <v>1428373</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
-        <v>352.036</v>
+        <v>2</v>
       </c>
       <c r="O31" s="7"/>
     </row>
@@ -2203,38 +2200,38 @@
         <v>6</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D32" s="8">
-        <v>46030.408148148148</v>
+        <v>46027.4840625</v>
       </c>
       <c r="E32" s="8">
-        <v>46030.408148148148</v>
+        <v>46027.4840625</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I32" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
-        <v>352.036</v>
+        <v>3</v>
       </c>
       <c r="O32" s="7"/>
     </row>
@@ -2247,35 +2244,35 @@
         <v>17</v>
       </c>
       <c r="D33" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="E33" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I33" s="7">
         <v>1394724</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
-        <v>352.036</v>
+        <v>4</v>
       </c>
       <c r="O33" s="7"/>
     </row>
@@ -2288,35 +2285,35 @@
         <v>17</v>
       </c>
       <c r="D34" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="E34" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I34" s="7">
         <v>1394724</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
-        <v>176.018</v>
+        <v>4</v>
       </c>
       <c r="O34" s="7"/>
     </row>
@@ -2326,38 +2323,38 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D35" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="E35" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
-        <v>528.05399999999997</v>
+        <v>4</v>
       </c>
       <c r="O35" s="7"/>
     </row>
@@ -2367,38 +2364,38 @@
         <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D36" s="8">
-        <v>46043.385474537034</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="E36" s="8">
-        <v>46043.385474537034</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
-        <v>264.02699999999999</v>
+        <v>2</v>
       </c>
       <c r="O36" s="7"/>
     </row>
@@ -2408,38 +2405,38 @@
         <v>6</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D37" s="8">
-        <v>46043.565196759257</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="E37" s="8">
-        <v>46043.565196759257</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I37" s="7">
         <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
-        <v>264.02699999999999</v>
+        <v>6</v>
       </c>
       <c r="O37" s="7"/>
     </row>
@@ -2452,35 +2449,35 @@
         <v>30</v>
       </c>
       <c r="D38" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="E38" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I38" s="7">
-        <v>1421099</v>
+        <v>1394724</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
-        <v>221</v>
+        <v>3</v>
       </c>
       <c r="O38" s="7"/>
     </row>
@@ -2490,38 +2487,38 @@
         <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D39" s="8">
-        <v>46078.552407407406</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="E39" s="8">
-        <v>46078.552407407406</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I39" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>261.11500000000001</v>
+        <v>3</v>
       </c>
       <c r="O39" s="7"/>
     </row>
@@ -2534,35 +2531,35 @@
         <v>31</v>
       </c>
       <c r="D40" s="8">
-        <v>46080.522418981483</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="E40" s="8">
-        <v>46080.522418981483</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I40" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>313.33799999999997</v>
+        <v>5</v>
       </c>
       <c r="O40" s="7"/>
     </row>
@@ -2572,38 +2569,38 @@
         <v>6</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D41" s="8">
-        <v>46080.532164351855</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="E41" s="8">
-        <v>46080.532164351855</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I41" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <v>470.00700000000001</v>
+        <v>5</v>
       </c>
       <c r="O41" s="7"/>
     </row>
@@ -2613,161 +2610,161 @@
         <v>6</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D42" s="8">
-        <v>46083.531342592592</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="E42" s="8">
-        <v>46083.531342592592</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I42" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>156.66899999999998</v>
+        <v>6</v>
       </c>
       <c r="O42" s="7"/>
     </row>
     <row r="43" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D43" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="E43" s="8">
-        <v>46035.47824074074</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I43" s="7">
-        <v>1404958</v>
+        <v>1422285</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <v>264.02699999999999</v>
+        <v>9</v>
       </c>
       <c r="O43" s="7"/>
     </row>
     <row r="44" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D44" s="8">
-        <v>46043.385196759256</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="E44" s="8">
-        <v>46043.385196759256</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I44" s="7">
-        <v>1405794</v>
+        <v>1422283</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>352.036</v>
+        <v>3</v>
       </c>
       <c r="O44" s="7"/>
     </row>
     <row r="45" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D45" s="8">
-        <v>46043.385289351849</v>
+        <v>46085.365902777776</v>
       </c>
       <c r="E45" s="8">
-        <v>46043.385289351849</v>
+        <v>46085.365902777776</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I45" s="7">
-        <v>1405794</v>
+        <v>1422283</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <v>176.018</v>
+        <v>2</v>
       </c>
       <c r="O45" s="7"/>
     </row>
@@ -2777,38 +2774,38 @@
         <v>7</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D46" s="8">
-        <v>46043.441296296296</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E46" s="8">
-        <v>46043.441296296296</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I46" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
-        <v>264.02699999999999</v>
+        <v>3</v>
       </c>
       <c r="O46" s="7"/>
     </row>
@@ -2818,38 +2815,38 @@
         <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D47" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E47" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I47" s="7">
         <v>1405794</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <v>176.018</v>
+        <v>4</v>
       </c>
       <c r="O47" s="7"/>
     </row>
@@ -2859,38 +2856,38 @@
         <v>7</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D48" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E48" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I48" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
-        <v>626.67599999999993</v>
+        <v>2</v>
       </c>
       <c r="O48" s="7"/>
     </row>
@@ -2900,38 +2897,38 @@
         <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D49" s="8">
-        <v>46051.280300925922</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E49" s="8">
-        <v>46051.280300925922</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I49" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <v>261.11500000000001</v>
+        <v>3</v>
       </c>
       <c r="O49" s="7"/>
     </row>
@@ -2944,35 +2941,35 @@
         <v>33</v>
       </c>
       <c r="D50" s="8">
-        <v>46056.33489583333</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E50" s="8">
-        <v>46056.33489583333</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I50" s="7">
-        <v>1410338</v>
+        <v>1405794</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
-        <v>451</v>
+        <v>2</v>
       </c>
       <c r="O50" s="7"/>
     </row>
@@ -2982,38 +2979,38 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D51" s="8">
-        <v>46062.345243055555</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E51" s="8">
-        <v>46062.345243055555</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I51" s="7">
-        <v>1412987</v>
+        <v>1411351</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
-        <v>265.20000000000005</v>
+        <v>12</v>
       </c>
       <c r="O51" s="7"/>
     </row>
@@ -3023,38 +3020,38 @@
         <v>7</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D52" s="8">
-        <v>46064.292500000003</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E52" s="8">
-        <v>46064.292500000003</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I52" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <v>132.60000000000002</v>
+        <v>5</v>
       </c>
       <c r="O52" s="7"/>
     </row>
@@ -3064,38 +3061,38 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D53" s="8">
-        <v>46073.402627314812</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E53" s="8">
-        <v>46073.402627314812</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I53" s="7">
-        <v>1421099</v>
+        <v>1410338</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
-        <v>88.4</v>
+        <v>10</v>
       </c>
       <c r="O53" s="7"/>
     </row>
@@ -3105,38 +3102,38 @@
         <v>7</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D54" s="8">
-        <v>46077.368379629632</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E54" s="8">
-        <v>46077.368379629632</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I54" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
-        <v>156.66899999999998</v>
+        <v>6</v>
       </c>
       <c r="O54" s="7"/>
     </row>
@@ -3146,248 +3143,248 @@
         <v>7</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D55" s="8">
-        <v>46077.554594907408</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E55" s="8">
-        <v>46077.554594907408</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I55" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <v>156.66899999999998</v>
+        <v>3</v>
       </c>
       <c r="O55" s="7"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A56" s="4"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="11">
-        <v>0</v>
-      </c>
-      <c r="N56" s="11">
-        <v>12817.616999999998</v>
-      </c>
-      <c r="O56" s="9">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
+    <row r="56" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A56" s="2"/>
+      <c r="B56" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" s="8">
+        <v>46073.402627314812</v>
+      </c>
+      <c r="E56" s="8">
+        <v>46073.402627314812</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I56" s="7">
+        <v>1421099</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10">
         <v>2</v>
       </c>
-      <c r="B57" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
-      <c r="L57" s="13"/>
-      <c r="M57" s="13"/>
-      <c r="N57" s="13"/>
-      <c r="O57" s="13"/>
+      <c r="O56" s="7"/>
+    </row>
+    <row r="57" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A57" s="2"/>
+      <c r="B57" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="E57" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I57" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10">
+        <v>3</v>
+      </c>
+      <c r="O57" s="7"/>
     </row>
     <row r="58" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D58" s="8">
-        <v>46027.666331018518</v>
+        <v>46077.554594907408</v>
       </c>
       <c r="E58" s="8">
-        <v>46027.666331018518</v>
+        <v>46077.554594907408</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I58" s="7">
-        <v>1386388</v>
+        <v>1422285</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>132.60000000000002</v>
+        <v>3</v>
       </c>
       <c r="O58" s="7"/>
     </row>
     <row r="59" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="8">
-        <v>46027.694131944445</v>
+        <v>46085.366041666668</v>
       </c>
       <c r="E59" s="8">
-        <v>46027.694131944445</v>
+        <v>46085.366041666668</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I59" s="7">
-        <v>1386388</v>
+        <v>1423125</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>44.2</v>
+        <v>5</v>
       </c>
       <c r="O59" s="7"/>
     </row>
-    <row r="60" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A60" s="2"/>
-      <c r="B60" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="E60" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="I60" s="7">
-        <v>1406206</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="K60" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="L60" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10">
-        <v>977.84499999999991</v>
-      </c>
-      <c r="O60" s="7"/>
-    </row>
-    <row r="61" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A61" s="2"/>
-      <c r="B61" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="8">
-        <v>46059.905682870369</v>
-      </c>
-      <c r="E61" s="8">
-        <v>46059.905682870369</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="I61" s="7">
-        <v>1411984</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K61" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="L61" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10">
-        <v>470.93400000000003</v>
-      </c>
-      <c r="O61" s="7"/>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A60" s="4"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="9">
+        <v>0</v>
+      </c>
+      <c r="N60" s="9">
+        <v>242</v>
+      </c>
+      <c r="O60" s="9">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
     </row>
     <row r="62" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
@@ -3395,38 +3392,38 @@
         <v>4</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D62" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E62" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I62" s="7">
-        <v>1411990</v>
+        <v>1386388</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>104.446</v>
+        <v>3</v>
       </c>
       <c r="O62" s="7"/>
     </row>
@@ -3436,38 +3433,38 @@
         <v>4</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D63" s="8">
-        <v>46065.655185185184</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E63" s="8">
-        <v>46065.655185185184</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I63" s="7">
-        <v>1411990</v>
+        <v>1386388</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M63" s="10"/>
       <c r="N63" s="10">
-        <v>104.446</v>
+        <v>1</v>
       </c>
       <c r="O63" s="7"/>
     </row>
@@ -3477,38 +3474,38 @@
         <v>4</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D64" s="8">
-        <v>46066.613657407404</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E64" s="8">
-        <v>46066.613657407404</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I64" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M64" s="10"/>
       <c r="N64" s="10">
-        <v>52.222999999999999</v>
+        <v>11</v>
       </c>
       <c r="O64" s="7"/>
     </row>
@@ -3518,38 +3515,38 @@
         <v>4</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D65" s="8">
-        <v>46066.670127314814</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E65" s="8">
-        <v>46066.670127314814</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I65" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>104.446</v>
+        <v>9</v>
       </c>
       <c r="O65" s="7"/>
     </row>
@@ -3559,284 +3556,284 @@
         <v>4</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D66" s="8">
-        <v>46079.703912037039</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E66" s="8">
-        <v>46079.703912037039</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I66" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>160.19999999999999</v>
+        <v>2</v>
       </c>
       <c r="O66" s="7"/>
     </row>
     <row r="67" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D67" s="8">
-        <v>46028.907905092594</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E67" s="8">
-        <v>46028.907905092594</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I67" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>663</v>
+        <v>2</v>
       </c>
       <c r="O67" s="7"/>
     </row>
     <row r="68" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D68" s="8">
-        <v>46029.6719212963</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E68" s="8">
-        <v>46029.6719212963</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I68" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>176.8</v>
+        <v>1</v>
       </c>
       <c r="O68" s="7"/>
     </row>
     <row r="69" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D69" s="8">
-        <v>46034.72855324074</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E69" s="8">
-        <v>46034.72855324074</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I69" s="7">
-        <v>1394721</v>
+        <v>1411990</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>132.60000000000002</v>
+        <v>2</v>
       </c>
       <c r="O69" s="7"/>
     </row>
     <row r="70" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D70" s="8">
-        <v>46037.838958333334</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E70" s="8">
-        <v>46037.838958333334</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I70" s="7">
-        <v>1394721</v>
+        <v>1410767</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>618.80000000000007</v>
+        <v>6</v>
       </c>
       <c r="O70" s="7"/>
     </row>
     <row r="71" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D71" s="8">
-        <v>46042.727754629632</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="E71" s="8">
-        <v>46042.727754629632</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I71" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>44.2</v>
+        <v>9</v>
       </c>
       <c r="O71" s="7"/>
     </row>
     <row r="72" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D72" s="8">
-        <v>46043.627881944441</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="E72" s="8">
-        <v>46043.627881944441</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I72" s="7">
-        <v>1410339</v>
+        <v>1428327</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>98</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>45.1</v>
+        <v>1</v>
       </c>
       <c r="O72" s="7"/>
     </row>
@@ -3846,38 +3843,38 @@
         <v>5</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D73" s="8">
-        <v>46052.626018518517</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E73" s="8">
-        <v>46052.626018518517</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I73" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L73" s="7" t="s">
         <v>112</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>90.168000000000006</v>
+        <v>15</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3887,38 +3884,38 @@
         <v>5</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D74" s="8">
-        <v>46053.632291666669</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E74" s="8">
-        <v>46053.632291666669</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I74" s="7">
-        <v>1411708</v>
+        <v>1394721</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L74" s="7" t="s">
         <v>112</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>405.75600000000003</v>
+        <v>4</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3928,38 +3925,38 @@
         <v>5</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D75" s="8">
-        <v>46071.601446759261</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E75" s="8">
-        <v>46071.601446759261</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I75" s="7">
-        <v>1418251</v>
+        <v>1394721</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>77.8</v>
+        <v>3</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3969,38 +3966,38 @@
         <v>5</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D76" s="8">
-        <v>46076.679282407407</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E76" s="8">
-        <v>46076.679282407407</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I76" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>45.1</v>
+        <v>14</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -4010,38 +4007,38 @@
         <v>5</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D77" s="8">
-        <v>46077.591944444444</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E77" s="8">
-        <v>46077.591944444444</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I77" s="7">
-        <v>1422511</v>
+        <v>1394721</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>180.4</v>
+        <v>1</v>
       </c>
       <c r="O77" s="7"/>
     </row>
@@ -4051,284 +4048,284 @@
         <v>5</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D78" s="8">
-        <v>46077.861296296294</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E78" s="8">
-        <v>46077.861296296294</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I78" s="7">
-        <v>1422511</v>
+        <v>1410339</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>541.20000000000005</v>
+        <v>1</v>
       </c>
       <c r="O78" s="7"/>
     </row>
     <row r="79" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D79" s="8">
-        <v>46027.633611111109</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E79" s="8">
-        <v>46027.633611111109</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I79" s="7">
-        <v>1404289</v>
+        <v>1411706</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>264.02699999999999</v>
+        <v>2</v>
       </c>
       <c r="O79" s="7"/>
     </row>
     <row r="80" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="D80" s="8">
-        <v>46029.802372685182</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E80" s="8">
-        <v>46029.802372685182</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I80" s="7">
-        <v>1394724</v>
+        <v>1411708</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>880.09</v>
+        <v>9</v>
       </c>
       <c r="O80" s="7"/>
     </row>
     <row r="81" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D81" s="8">
-        <v>46030.908472222225</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E81" s="8">
-        <v>46030.908472222225</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I81" s="7">
-        <v>1394724</v>
+        <v>1418251</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K81" s="5" t="s">
         <v>107</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
-        <v>440.04500000000002</v>
+        <v>1</v>
       </c>
       <c r="O81" s="7"/>
     </row>
     <row r="82" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D82" s="8">
-        <v>46031.590057870373</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E82" s="8">
-        <v>46031.590057870373</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I82" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K82" s="5" t="s">
         <v>107</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>352.036</v>
+        <v>1</v>
       </c>
       <c r="O82" s="7"/>
     </row>
     <row r="83" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D83" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E83" s="8">
-        <v>46076.8827662037</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I83" s="7">
-        <v>1422286</v>
+        <v>1422511</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K83" s="5" t="s">
         <v>107</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>783.34500000000003</v>
+        <v>4</v>
       </c>
       <c r="O83" s="7"/>
     </row>
     <row r="84" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D84" s="8">
-        <v>46078.867326388892</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E84" s="8">
-        <v>46078.867326388892</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I84" s="7">
-        <v>1422286</v>
+        <v>1422511</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K84" s="5" t="s">
         <v>107</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>208.892</v>
+        <v>12</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4338,38 +4335,38 @@
         <v>6</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D85" s="8">
-        <v>46080.639293981483</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E85" s="8">
-        <v>46080.639293981483</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I85" s="7">
-        <v>1422285</v>
+        <v>1404289</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>104.446</v>
+        <v>3</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4379,38 +4376,38 @@
         <v>6</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D86" s="8">
-        <v>46080.716932870368</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E86" s="8">
-        <v>46080.716932870368</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I86" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>52.222999999999999</v>
+        <v>10</v>
       </c>
       <c r="O86" s="7"/>
     </row>
@@ -4420,38 +4417,38 @@
         <v>6</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D87" s="8">
-        <v>46080.740543981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E87" s="8">
-        <v>46080.740543981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I87" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>52.222999999999999</v>
+        <v>5</v>
       </c>
       <c r="O87" s="7"/>
     </row>
@@ -4461,38 +4458,38 @@
         <v>6</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D88" s="8">
-        <v>46081.588483796295</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E88" s="8">
-        <v>46081.588483796295</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I88" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>91</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>52.222999999999999</v>
+        <v>4</v>
       </c>
       <c r="O88" s="7"/>
     </row>
@@ -4502,284 +4499,284 @@
         <v>6</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D89" s="8">
-        <v>46083.87841435185</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E89" s="8">
-        <v>46083.87841435185</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I89" s="7">
-        <v>1422283</v>
+        <v>1422286</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>2350.0349999999999</v>
+        <v>15</v>
       </c>
       <c r="O89" s="7"/>
     </row>
     <row r="90" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D90" s="8">
-        <v>46024.795127314814</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E90" s="8">
-        <v>46024.795127314814</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I90" s="7">
-        <v>1398335</v>
+        <v>1422286</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>265.20000000000005</v>
+        <v>4</v>
       </c>
       <c r="O90" s="7"/>
     </row>
     <row r="91" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D91" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E91" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I91" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>88.4</v>
+        <v>2</v>
       </c>
       <c r="O91" s="7"/>
     </row>
     <row r="92" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D92" s="8">
-        <v>46024.900324074071</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E92" s="8">
-        <v>46024.900324074071</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I92" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>221</v>
+        <v>1</v>
       </c>
       <c r="O92" s="7"/>
     </row>
     <row r="93" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D93" s="8">
-        <v>46028.866898148146</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E93" s="8">
-        <v>46028.866898148146</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I93" s="7">
-        <v>1402956</v>
+        <v>1422285</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>90.168000000000006</v>
+        <v>1</v>
       </c>
       <c r="O93" s="7"/>
     </row>
     <row r="94" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D94" s="8">
-        <v>46034.751261574071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E94" s="8">
-        <v>46034.751261574071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I94" s="7">
-        <v>1404958</v>
+        <v>1422285</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>616.06299999999999</v>
+        <v>1</v>
       </c>
       <c r="O94" s="7"/>
     </row>
     <row r="95" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D95" s="8">
-        <v>46062.904895833337</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E95" s="8">
-        <v>46062.904895833337</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I95" s="7">
-        <v>1412987</v>
+        <v>1422283</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>44.2</v>
+        <v>45</v>
       </c>
       <c r="O95" s="7"/>
     </row>
@@ -4789,38 +4786,38 @@
         <v>7</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D96" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E96" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I96" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>221</v>
+        <v>6</v>
       </c>
       <c r="O96" s="7"/>
     </row>
@@ -4830,38 +4827,38 @@
         <v>7</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D97" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E97" s="8">
-        <v>46067.906875000001</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I97" s="7">
-        <v>1411991</v>
+        <v>1398335</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>156.66899999999998</v>
+        <v>2</v>
       </c>
       <c r="O97" s="7"/>
     </row>
@@ -4871,38 +4868,38 @@
         <v>7</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D98" s="8">
-        <v>46069.700543981482</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E98" s="8">
-        <v>46069.700543981482</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I98" s="7">
-        <v>1411991</v>
+        <v>1398335</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
-        <v>522.23</v>
+        <v>5</v>
       </c>
       <c r="O98" s="7"/>
     </row>
@@ -4912,38 +4909,38 @@
         <v>7</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D99" s="8">
-        <v>46077.65824074074</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E99" s="8">
-        <v>46077.65824074074</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I99" s="7">
-        <v>1422285</v>
+        <v>1402956</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10">
-        <v>52.222999999999999</v>
+        <v>2</v>
       </c>
       <c r="O99" s="7"/>
     </row>
@@ -4953,38 +4950,38 @@
         <v>7</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D100" s="8">
-        <v>46078.881018518521</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E100" s="8">
-        <v>46078.881018518521</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I100" s="7">
-        <v>1423123</v>
+        <v>1404958</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10">
-        <v>44.2</v>
+        <v>7</v>
       </c>
       <c r="O100" s="7"/>
     </row>
@@ -4994,87 +4991,333 @@
         <v>7</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D101" s="8">
-        <v>46079.901782407411</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E101" s="8">
-        <v>46079.901782407411</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I101" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10">
-        <v>44.2</v>
+        <v>1</v>
       </c>
       <c r="O101" s="7"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A102" s="4"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102" s="11">
+    <row r="102" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A102" s="2"/>
+      <c r="B102" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D102" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="E102" s="8">
+        <v>46063.874467592592</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I102" s="7">
+        <v>1412987</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K102" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L102" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M102" s="10"/>
+      <c r="N102" s="10">
+        <v>5</v>
+      </c>
+      <c r="O102" s="7"/>
+    </row>
+    <row r="103" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A103" s="2"/>
+      <c r="B103" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="E103" s="8">
+        <v>46067.906875000001</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I103" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K103" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L103" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M103" s="10"/>
+      <c r="N103" s="10">
+        <v>3</v>
+      </c>
+      <c r="O103" s="7"/>
+    </row>
+    <row r="104" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A104" s="2"/>
+      <c r="B104" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D104" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E104" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I104" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="K104" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L104" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M104" s="10"/>
+      <c r="N104" s="10">
+        <v>10</v>
+      </c>
+      <c r="O104" s="7"/>
+    </row>
+    <row r="105" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A105" s="2"/>
+      <c r="B105" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E105" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I105" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K105" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="M105" s="10"/>
+      <c r="N105" s="10">
+        <v>1</v>
+      </c>
+      <c r="O105" s="7"/>
+    </row>
+    <row r="106" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A106" s="2"/>
+      <c r="B106" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D106" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E106" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I106" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K106" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L106" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10">
+        <v>1</v>
+      </c>
+      <c r="O106" s="7"/>
+    </row>
+    <row r="107" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A107" s="2"/>
+      <c r="B107" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D107" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E107" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I107" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K107" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L107" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="M107" s="10"/>
+      <c r="N107" s="10">
+        <v>1</v>
+      </c>
+      <c r="O107" s="7"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A108" s="4"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="9">
         <v>0</v>
       </c>
-      <c r="N102" s="11">
-        <v>13077.402000000002</v>
-      </c>
-      <c r="O102" s="9">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A103" s="4"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="9">
-        <v>96</v>
-      </c>
-      <c r="I103" s="6"/>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6"/>
-      <c r="L103" s="6"/>
-      <c r="M103" s="11">
+      <c r="N108" s="9">
+        <v>249</v>
+      </c>
+      <c r="O108" s="9">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A109" s="4"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="9">
+        <v>102</v>
+      </c>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="9">
         <v>0</v>
       </c>
-      <c r="N103" s="11">
-        <v>25895.019000000018</v>
-      </c>
-      <c r="O103" s="9">
-        <v>96</v>
+      <c r="N109" s="9">
+        <v>491</v>
+      </c>
+      <c r="O109" s="9">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -5084,7 +5327,7 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B57:O57"/>
+    <mergeCell ref="B61:O61"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F858FCC-9CE8-4CA4-92C5-9A807034D2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0903554-4587-48B6-9CDA-69D4BBD6EFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{463ADD43-9B69-45E4-B575-83E842D7E9F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDC75864-2D3A-426D-8A84-ED2527537ED9}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="125">
   <si>
     <t>Dados</t>
   </si>
@@ -70,6 +70,9 @@
     <t>11/02/2026</t>
   </si>
   <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
     <t>06/01/2026</t>
   </si>
   <si>
@@ -268,6 +271,9 @@
     <t>CIPF002324-PEPPA_26-24 - GARRAFA CILINDRICA DEC 280ML - PEPPA 202</t>
   </si>
   <si>
+    <t>CIPF002325-JARD-ENC_26-24 - GARRAFA CILINDRICA DEC 480ML - IMPRESSÃO</t>
+  </si>
+  <si>
     <t>CI002027-FROZEN_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - FROZEN</t>
   </si>
   <si>
@@ -314,9 +320,6 @@
   </si>
   <si>
     <t xml:space="preserve">CI002027-ARIEL_23-24 - CORPO GARRAFA RETRÔ 500ML SOPRO - ARIEL </t>
-  </si>
-  <si>
-    <t>CIPF002325-JARD-ENC_26-24 - GARRAFA CILINDRICA DEC 480ML - IMPRESSÃO</t>
   </si>
   <si>
     <t>CIPF002816-FITNESS_F-732 - CORPO GARRAFA FUN 600 ML - FITNESS F - I</t>
@@ -936,8 +939,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB9BE098-F4B4-4F86-9F10-454FDC02BB27}">
-  <dimension ref="A1:O109"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874E1856-81A4-4324-B49F-EF2BFD955075}">
+  <dimension ref="A1:O113"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -968,14 +971,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -989,40 +992,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1061,25 +1064,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1102,25 +1105,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1143,25 +1146,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1184,25 +1187,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1225,25 +1228,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1266,25 +1269,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1307,25 +1310,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1348,25 +1351,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1389,25 +1392,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1418,41 +1421,41 @@
     <row r="13" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="8">
-        <v>46028.331469907411</v>
+        <v>46086.442870370367</v>
       </c>
       <c r="E13" s="8">
-        <v>46028.331469907411</v>
+        <v>46086.442870370367</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I13" s="7">
-        <v>1402958</v>
+        <v>1428327</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O13" s="7"/>
     </row>
@@ -1465,35 +1468,35 @@
         <v>17</v>
       </c>
       <c r="D14" s="8">
-        <v>46030.306192129632</v>
+        <v>46028.331469907411</v>
       </c>
       <c r="E14" s="8">
-        <v>46030.306192129632</v>
+        <v>46028.331469907411</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I14" s="7">
-        <v>1394721</v>
+        <v>1402958</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O14" s="7"/>
     </row>
@@ -1506,35 +1509,35 @@
         <v>18</v>
       </c>
       <c r="D15" s="8">
-        <v>46031.443101851852</v>
+        <v>46030.306192129632</v>
       </c>
       <c r="E15" s="8">
-        <v>46031.443101851852</v>
+        <v>46030.306192129632</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O15" s="7"/>
     </row>
@@ -1547,35 +1550,35 @@
         <v>19</v>
       </c>
       <c r="D16" s="8">
-        <v>46035.530381944445</v>
+        <v>46031.443101851852</v>
       </c>
       <c r="E16" s="8">
-        <v>46035.530381944445</v>
+        <v>46031.443101851852</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O16" s="7"/>
     </row>
@@ -1585,38 +1588,38 @@
         <v>5</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D17" s="8">
-        <v>46046.391701388886</v>
+        <v>46035.530381944445</v>
       </c>
       <c r="E17" s="8">
-        <v>46046.391701388886</v>
+        <v>46035.530381944445</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I17" s="7">
-        <v>1410340</v>
+        <v>1394721</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" s="7"/>
     </row>
@@ -1629,31 +1632,31 @@
         <v>10</v>
       </c>
       <c r="D18" s="8">
-        <v>46046.516597222224</v>
+        <v>46046.391701388886</v>
       </c>
       <c r="E18" s="8">
-        <v>46046.516597222224</v>
+        <v>46046.391701388886</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1667,38 +1670,38 @@
         <v>5</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D19" s="8">
-        <v>46048.278912037036</v>
+        <v>46046.516597222224</v>
       </c>
       <c r="E19" s="8">
-        <v>46048.278912037036</v>
+        <v>46046.516597222224</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="7"/>
     </row>
@@ -1708,38 +1711,38 @@
         <v>5</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D20" s="8">
-        <v>46051.403391203705</v>
+        <v>46048.278912037036</v>
       </c>
       <c r="E20" s="8">
-        <v>46051.403391203705</v>
+        <v>46048.278912037036</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O20" s="7"/>
     </row>
@@ -1749,38 +1752,38 @@
         <v>5</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" s="8">
-        <v>46053.550381944442</v>
+        <v>46051.403391203705</v>
       </c>
       <c r="E21" s="8">
-        <v>46053.550381944442</v>
+        <v>46051.403391203705</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I21" s="7">
-        <v>1411706</v>
+        <v>1410340</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>84</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O21" s="7"/>
     </row>
@@ -1790,34 +1793,34 @@
         <v>5</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D22" s="8">
-        <v>46057.413171296299</v>
+        <v>46053.550381944442</v>
       </c>
       <c r="E22" s="8">
-        <v>46057.413171296299</v>
+        <v>46053.550381944442</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I22" s="7">
-        <v>1411704</v>
+        <v>1411706</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1834,35 +1837,35 @@
         <v>22</v>
       </c>
       <c r="D23" s="8">
-        <v>46058.357476851852</v>
+        <v>46057.413171296299</v>
       </c>
       <c r="E23" s="8">
-        <v>46058.357476851852</v>
+        <v>46057.413171296299</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O23" s="7"/>
     </row>
@@ -1872,38 +1875,38 @@
         <v>5</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" s="8">
-        <v>46058.531793981485</v>
+        <v>46058.357476851852</v>
       </c>
       <c r="E24" s="8">
-        <v>46058.531793981485</v>
+        <v>46058.357476851852</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="7"/>
     </row>
@@ -1916,35 +1919,35 @@
         <v>23</v>
       </c>
       <c r="D25" s="8">
-        <v>46067.433020833334</v>
+        <v>46058.531793981485</v>
       </c>
       <c r="E25" s="8">
-        <v>46067.433020833334</v>
+        <v>46058.531793981485</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I25" s="7">
-        <v>1418256</v>
+        <v>1411704</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>108</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O25" s="7"/>
     </row>
@@ -1957,35 +1960,35 @@
         <v>24</v>
       </c>
       <c r="D26" s="8">
-        <v>46073.579664351855</v>
+        <v>46067.433020833334</v>
       </c>
       <c r="E26" s="8">
-        <v>46073.579664351855</v>
+        <v>46067.433020833334</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I26" s="7">
-        <v>1422511</v>
+        <v>1418256</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O26" s="7"/>
     </row>
@@ -1998,35 +2001,35 @@
         <v>25</v>
       </c>
       <c r="D27" s="8">
-        <v>46077.38318287037</v>
+        <v>46073.579664351855</v>
       </c>
       <c r="E27" s="8">
-        <v>46077.38318287037</v>
+        <v>46073.579664351855</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="O27" s="7"/>
     </row>
@@ -2039,35 +2042,35 @@
         <v>26</v>
       </c>
       <c r="D28" s="8">
-        <v>46078.372766203705</v>
+        <v>46077.38318287037</v>
       </c>
       <c r="E28" s="8">
-        <v>46078.372766203705</v>
+        <v>46077.38318287037</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O28" s="7"/>
     </row>
@@ -2080,35 +2083,35 @@
         <v>27</v>
       </c>
       <c r="D29" s="8">
-        <v>46083.272581018522</v>
+        <v>46078.372766203705</v>
       </c>
       <c r="E29" s="8">
-        <v>46083.272581018522</v>
+        <v>46078.372766203705</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I29" s="7">
-        <v>1423124</v>
+        <v>1422511</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O29" s="7"/>
     </row>
@@ -2121,35 +2124,35 @@
         <v>28</v>
       </c>
       <c r="D30" s="8">
-        <v>46085.323807870373</v>
+        <v>46083.272581018522</v>
       </c>
       <c r="E30" s="8">
-        <v>46085.323807870373</v>
+        <v>46083.272581018522</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I30" s="7">
-        <v>1428373</v>
+        <v>1423124</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" s="7"/>
     </row>
@@ -2159,34 +2162,34 @@
         <v>5</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D31" s="8">
-        <v>46085.344675925924</v>
+        <v>46085.323807870373</v>
       </c>
       <c r="E31" s="8">
-        <v>46085.344675925924</v>
+        <v>46085.323807870373</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I31" s="7">
         <v>1428373</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2197,69 +2200,69 @@
     <row r="32" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D32" s="8">
-        <v>46027.4840625</v>
+        <v>46085.344675925924</v>
       </c>
       <c r="E32" s="8">
-        <v>46027.4840625</v>
+        <v>46085.344675925924</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I32" s="7">
-        <v>1404289</v>
+        <v>1428373</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>108</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O32" s="7"/>
     </row>
     <row r="33" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D33" s="8">
-        <v>46030.397997685184</v>
+        <v>46086.434641203705</v>
       </c>
       <c r="E33" s="8">
-        <v>46030.397997685184</v>
+        <v>46086.434641203705</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I33" s="7">
-        <v>1394724</v>
+        <v>1428373</v>
       </c>
       <c r="J33" s="5" t="s">
         <v>91</v>
@@ -2268,11 +2271,11 @@
         <v>108</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O33" s="7"/>
     </row>
@@ -2282,38 +2285,38 @@
         <v>6</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D34" s="8">
-        <v>46030.408148148148</v>
+        <v>46027.4840625</v>
       </c>
       <c r="E34" s="8">
-        <v>46030.408148148148</v>
+        <v>46027.4840625</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I34" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O34" s="7"/>
     </row>
@@ -2323,34 +2326,34 @@
         <v>6</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="E35" s="8">
-        <v>46030.478854166664</v>
+        <v>46030.397997685184</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2364,38 +2367,38 @@
         <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="E36" s="8">
-        <v>46030.561284722222</v>
+        <v>46030.408148148148</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O36" s="7"/>
     </row>
@@ -2405,38 +2408,38 @@
         <v>6</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="E37" s="8">
-        <v>46035.478368055556</v>
+        <v>46030.478854166664</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I37" s="7">
         <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O37" s="7"/>
     </row>
@@ -2446,38 +2449,38 @@
         <v>6</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D38" s="8">
-        <v>46043.385474537034</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="E38" s="8">
-        <v>46043.385474537034</v>
+        <v>46030.561284722222</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I38" s="7">
         <v>1394724</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O38" s="7"/>
     </row>
@@ -2487,38 +2490,38 @@
         <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D39" s="8">
-        <v>46043.565196759257</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="E39" s="8">
-        <v>46043.565196759257</v>
+        <v>46035.478368055556</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I39" s="7">
         <v>1394724</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O39" s="7"/>
     </row>
@@ -2531,35 +2534,35 @@
         <v>31</v>
       </c>
       <c r="D40" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="E40" s="8">
-        <v>46069.559953703705</v>
+        <v>46043.385474537034</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I40" s="7">
-        <v>1421099</v>
+        <v>1394724</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O40" s="7"/>
     </row>
@@ -2569,38 +2572,38 @@
         <v>6</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D41" s="8">
-        <v>46078.552407407406</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="E41" s="8">
-        <v>46078.552407407406</v>
+        <v>46043.565196759257</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I41" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>93</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O41" s="7"/>
     </row>
@@ -2613,35 +2616,35 @@
         <v>32</v>
       </c>
       <c r="D42" s="8">
-        <v>46080.522418981483</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="E42" s="8">
-        <v>46080.522418981483</v>
+        <v>46069.559953703705</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I42" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>94</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O42" s="7"/>
     </row>
@@ -2651,28 +2654,28 @@
         <v>6</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D43" s="8">
-        <v>46080.532164351855</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="E43" s="8">
-        <v>46080.532164351855</v>
+        <v>46078.552407407406</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I43" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K43" s="5" t="s">
         <v>108</v>
@@ -2682,7 +2685,7 @@
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O43" s="7"/>
     </row>
@@ -2692,38 +2695,38 @@
         <v>6</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D44" s="8">
-        <v>46083.531342592592</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="E44" s="8">
-        <v>46083.531342592592</v>
+        <v>46080.522418981483</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I44" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O44" s="7"/>
     </row>
@@ -2733,75 +2736,75 @@
         <v>6</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D45" s="8">
-        <v>46085.365902777776</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="E45" s="8">
-        <v>46085.365902777776</v>
+        <v>46080.532164351855</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I45" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O45" s="7"/>
     </row>
     <row r="46" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D46" s="8">
-        <v>46035.47824074074</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="E46" s="8">
-        <v>46035.47824074074</v>
+        <v>46083.531342592592</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I46" s="7">
-        <v>1404958</v>
+        <v>1422283</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2812,82 +2815,82 @@
     <row r="47" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D47" s="8">
-        <v>46043.385196759256</v>
+        <v>46085.365902777776</v>
       </c>
       <c r="E47" s="8">
-        <v>46043.385196759256</v>
+        <v>46085.365902777776</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I47" s="7">
-        <v>1405794</v>
+        <v>1422283</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O47" s="7"/>
     </row>
     <row r="48" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D48" s="8">
-        <v>46043.385289351849</v>
+        <v>46086.317847222221</v>
       </c>
       <c r="E48" s="8">
-        <v>46043.385289351849</v>
+        <v>46086.317847222221</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>75</v>
       </c>
       <c r="I48" s="7">
-        <v>1405794</v>
+        <v>1428242</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O48" s="7"/>
     </row>
@@ -2897,34 +2900,34 @@
         <v>7</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D49" s="8">
-        <v>46043.441296296296</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E49" s="8">
-        <v>46043.441296296296</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I49" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
@@ -2938,38 +2941,38 @@
         <v>7</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D50" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E50" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I50" s="7">
         <v>1405794</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O50" s="7"/>
     </row>
@@ -2979,38 +2982,38 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D51" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E51" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I51" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O51" s="7"/>
     </row>
@@ -3020,38 +3023,38 @@
         <v>7</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D52" s="8">
-        <v>46051.280300925922</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E52" s="8">
-        <v>46051.280300925922</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I52" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O52" s="7"/>
     </row>
@@ -3064,35 +3067,35 @@
         <v>34</v>
       </c>
       <c r="D53" s="8">
-        <v>46056.33489583333</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E53" s="8">
-        <v>46056.33489583333</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I53" s="7">
-        <v>1410338</v>
+        <v>1405794</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O53" s="7"/>
     </row>
@@ -3102,38 +3105,38 @@
         <v>7</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D54" s="8">
-        <v>46062.345243055555</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E54" s="8">
-        <v>46062.345243055555</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I54" s="7">
-        <v>1412987</v>
+        <v>1411351</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O54" s="7"/>
     </row>
@@ -3143,38 +3146,38 @@
         <v>7</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D55" s="8">
-        <v>46064.292500000003</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E55" s="8">
-        <v>46064.292500000003</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I55" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O55" s="7"/>
     </row>
@@ -3184,38 +3187,38 @@
         <v>7</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D56" s="8">
-        <v>46073.402627314812</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E56" s="8">
-        <v>46073.402627314812</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I56" s="7">
-        <v>1421099</v>
+        <v>1410338</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O56" s="7"/>
     </row>
@@ -3225,38 +3228,38 @@
         <v>7</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D57" s="8">
-        <v>46077.368379629632</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E57" s="8">
-        <v>46077.368379629632</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I57" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O57" s="7"/>
     </row>
@@ -3266,34 +3269,34 @@
         <v>7</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D58" s="8">
-        <v>46077.554594907408</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E58" s="8">
-        <v>46077.554594907408</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I58" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
@@ -3307,98 +3310,136 @@
         <v>7</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D59" s="8">
-        <v>46085.366041666668</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="E59" s="8">
-        <v>46085.366041666668</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I59" s="7">
-        <v>1423125</v>
+        <v>1421099</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O59" s="7"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A60" s="4"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="9">
-        <v>0</v>
-      </c>
-      <c r="N60" s="9">
-        <v>242</v>
-      </c>
-      <c r="O60" s="9">
+    <row r="60" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A60" s="2"/>
+      <c r="B60" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D60" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="E60" s="8">
+        <v>46077.368379629632</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I60" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10">
+        <v>3</v>
+      </c>
+      <c r="O60" s="7"/>
+    </row>
+    <row r="61" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A61" s="2"/>
+      <c r="B61" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="E61" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="12"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12"/>
-      <c r="L61" s="12"/>
-      <c r="M61" s="12"/>
-      <c r="N61" s="12"/>
-      <c r="O61" s="12"/>
+      <c r="G61" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I61" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10">
+        <v>3</v>
+      </c>
+      <c r="O61" s="7"/>
     </row>
     <row r="62" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>29</v>
       </c>
       <c r="D62" s="8">
-        <v>46027.666331018518</v>
+        <v>46085.366041666668</v>
       </c>
       <c r="E62" s="8">
-        <v>46027.666331018518</v>
+        <v>46085.366041666668</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>62</v>
@@ -3407,107 +3448,69 @@
         <v>72</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I62" s="7">
-        <v>1386388</v>
+        <v>1423125</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K62" s="5" t="s">
         <v>109</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O62" s="7"/>
     </row>
-    <row r="63" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A63" s="2"/>
-      <c r="B63" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E63" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I63" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="K63" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="L63" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="M63" s="10"/>
-      <c r="N63" s="10">
-        <v>1</v>
-      </c>
-      <c r="O63" s="7"/>
-    </row>
-    <row r="64" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A64" s="2"/>
-      <c r="B64" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D64" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="E64" s="8">
-        <v>46036.841574074075</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I64" s="7">
-        <v>1406206</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K64" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="L64" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10">
-        <v>11</v>
-      </c>
-      <c r="O64" s="7"/>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A63" s="4"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="9">
+        <v>0</v>
+      </c>
+      <c r="N63" s="9">
+        <v>250</v>
+      </c>
+      <c r="O63" s="9">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="12"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="12"/>
     </row>
     <row r="65" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
@@ -3515,38 +3518,38 @@
         <v>4</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D65" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E65" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I65" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M65" s="10"/>
       <c r="N65" s="10">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O65" s="7"/>
     </row>
@@ -3556,38 +3559,38 @@
         <v>4</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D66" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E66" s="8">
-        <v>46064.60796296296</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I66" s="7">
-        <v>1411990</v>
+        <v>1386388</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>79</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L66" s="7" t="s">
         <v>113</v>
       </c>
       <c r="M66" s="10"/>
       <c r="N66" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" s="7"/>
     </row>
@@ -3597,38 +3600,38 @@
         <v>4</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D67" s="8">
-        <v>46065.655185185184</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E67" s="8">
-        <v>46065.655185185184</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I67" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O67" s="7"/>
     </row>
@@ -3638,38 +3641,38 @@
         <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D68" s="8">
-        <v>46066.613657407404</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E68" s="8">
-        <v>46066.613657407404</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I68" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3679,34 +3682,34 @@
         <v>4</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D69" s="8">
-        <v>46066.670127314814</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E69" s="8">
-        <v>46066.670127314814</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I69" s="7">
         <v>1411990</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
@@ -3720,38 +3723,38 @@
         <v>4</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D70" s="8">
-        <v>46079.703912037039</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E70" s="8">
-        <v>46079.703912037039</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>63</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I70" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3761,38 +3764,38 @@
         <v>4</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D71" s="8">
-        <v>46084.877986111111</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E71" s="8">
-        <v>46084.877986111111</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I71" s="7">
-        <v>1428327</v>
+        <v>1411990</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3802,161 +3805,161 @@
         <v>4</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D72" s="8">
-        <v>46084.883263888885</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E72" s="8">
-        <v>46084.883263888885</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I72" s="7">
-        <v>1428327</v>
+        <v>1411990</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" s="7"/>
     </row>
     <row r="73" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D73" s="8">
-        <v>46028.907905092594</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E73" s="8">
-        <v>46028.907905092594</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I73" s="7">
-        <v>1394721</v>
+        <v>1410767</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O73" s="7"/>
     </row>
     <row r="74" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D74" s="8">
-        <v>46029.6719212963</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="E74" s="8">
-        <v>46029.6719212963</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I74" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O74" s="7"/>
     </row>
     <row r="75" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D75" s="8">
-        <v>46034.72855324074</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="E75" s="8">
-        <v>46034.72855324074</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I75" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O75" s="7"/>
     </row>
@@ -3966,38 +3969,38 @@
         <v>5</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D76" s="8">
-        <v>46037.838958333334</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E76" s="8">
-        <v>46037.838958333334</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I76" s="7">
         <v>1394721</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O76" s="7"/>
     </row>
@@ -4007,38 +4010,38 @@
         <v>5</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D77" s="8">
-        <v>46042.727754629632</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E77" s="8">
-        <v>46042.727754629632</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I77" s="7">
         <v>1394721</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O77" s="7"/>
     </row>
@@ -4048,38 +4051,38 @@
         <v>5</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D78" s="8">
-        <v>46043.627881944441</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E78" s="8">
-        <v>46043.627881944441</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I78" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O78" s="7"/>
     </row>
@@ -4089,38 +4092,38 @@
         <v>5</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D79" s="8">
-        <v>46052.626018518517</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E79" s="8">
-        <v>46052.626018518517</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I79" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4130,38 +4133,38 @@
         <v>5</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="D80" s="8">
-        <v>46053.632291666669</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E80" s="8">
-        <v>46053.632291666669</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I80" s="7">
-        <v>1411708</v>
+        <v>1394721</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O80" s="7"/>
     </row>
@@ -4171,34 +4174,34 @@
         <v>5</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D81" s="8">
-        <v>46071.601446759261</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E81" s="8">
-        <v>46071.601446759261</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I81" s="7">
-        <v>1418251</v>
+        <v>1410339</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
@@ -4212,38 +4215,38 @@
         <v>5</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D82" s="8">
-        <v>46076.679282407407</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E82" s="8">
-        <v>46076.679282407407</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>63</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I82" s="7">
-        <v>1422511</v>
+        <v>1411706</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O82" s="7"/>
     </row>
@@ -4253,38 +4256,38 @@
         <v>5</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D83" s="8">
-        <v>46077.591944444444</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E83" s="8">
-        <v>46077.591944444444</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I83" s="7">
-        <v>1422511</v>
+        <v>1411708</v>
       </c>
       <c r="J83" s="5" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O83" s="7"/>
     </row>
@@ -4294,189 +4297,189 @@
         <v>5</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D84" s="8">
-        <v>46077.861296296294</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E84" s="8">
-        <v>46077.861296296294</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I84" s="7">
-        <v>1422511</v>
+        <v>1418251</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O84" s="7"/>
     </row>
     <row r="85" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D85" s="8">
-        <v>46027.633611111109</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E85" s="8">
-        <v>46027.633611111109</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I85" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O85" s="7"/>
     </row>
     <row r="86" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D86" s="8">
-        <v>46029.802372685182</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E86" s="8">
-        <v>46029.802372685182</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I86" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O86" s="7"/>
     </row>
     <row r="87" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D87" s="8">
-        <v>46030.908472222225</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E87" s="8">
-        <v>46030.908472222225</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H87" s="5" t="s">
         <v>75</v>
       </c>
       <c r="I87" s="7">
-        <v>1394724</v>
+        <v>1422511</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O87" s="7"/>
     </row>
     <row r="88" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D88" s="8">
-        <v>46031.590057870373</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="E88" s="8">
-        <v>46031.590057870373</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>75</v>
       </c>
       <c r="I88" s="7">
-        <v>1394724</v>
+        <v>1428373</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>91</v>
@@ -4485,11 +4488,11 @@
         <v>110</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O88" s="7"/>
     </row>
@@ -4499,38 +4502,38 @@
         <v>6</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D89" s="8">
-        <v>46076.8827662037</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E89" s="8">
-        <v>46076.8827662037</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I89" s="7">
-        <v>1422286</v>
+        <v>1404289</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O89" s="7"/>
     </row>
@@ -4540,38 +4543,38 @@
         <v>6</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D90" s="8">
-        <v>46078.867326388892</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E90" s="8">
-        <v>46078.867326388892</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I90" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J90" s="5" t="s">
         <v>93</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O90" s="7"/>
     </row>
@@ -4581,38 +4584,38 @@
         <v>6</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D91" s="8">
-        <v>46080.639293981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E91" s="8">
-        <v>46080.639293981483</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I91" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O91" s="7"/>
     </row>
@@ -4622,38 +4625,38 @@
         <v>6</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D92" s="8">
-        <v>46080.716932870368</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E92" s="8">
-        <v>46080.716932870368</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I92" s="7">
-        <v>1422285</v>
+        <v>1394724</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O92" s="7"/>
     </row>
@@ -4663,38 +4666,38 @@
         <v>6</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D93" s="8">
-        <v>46080.740543981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E93" s="8">
-        <v>46080.740543981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I93" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L93" s="7" t="s">
         <v>117</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="O93" s="7"/>
     </row>
@@ -4704,38 +4707,38 @@
         <v>6</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D94" s="8">
-        <v>46081.588483796295</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E94" s="8">
-        <v>46081.588483796295</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I94" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L94" s="7" t="s">
         <v>117</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O94" s="7"/>
     </row>
@@ -4745,202 +4748,202 @@
         <v>6</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D95" s="8">
-        <v>46083.87841435185</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E95" s="8">
-        <v>46083.87841435185</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I95" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="O95" s="7"/>
     </row>
     <row r="96" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D96" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E96" s="8">
-        <v>46024.795127314814</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>75</v>
       </c>
       <c r="I96" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O96" s="7"/>
     </row>
     <row r="97" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D97" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E97" s="8">
-        <v>46024.795277777775</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F97" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I97" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O97" s="7"/>
     </row>
     <row r="98" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D98" s="8">
-        <v>46024.900324074071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E98" s="8">
-        <v>46024.900324074071</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>75</v>
       </c>
       <c r="I98" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O98" s="7"/>
     </row>
     <row r="99" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D99" s="8">
-        <v>46028.866898148146</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E99" s="8">
-        <v>46028.866898148146</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>75</v>
       </c>
       <c r="I99" s="7">
-        <v>1402956</v>
+        <v>1422283</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O99" s="7"/>
     </row>
@@ -4950,38 +4953,38 @@
         <v>7</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D100" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E100" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>69</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I100" s="7">
-        <v>1404958</v>
+        <v>1398335</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O100" s="7"/>
     </row>
@@ -4991,38 +4994,38 @@
         <v>7</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D101" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E101" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I101" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O101" s="7"/>
     </row>
@@ -5035,31 +5038,31 @@
         <v>50</v>
       </c>
       <c r="D102" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E102" s="8">
-        <v>46063.874467592592</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I102" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M102" s="10"/>
       <c r="N102" s="10">
@@ -5073,38 +5076,38 @@
         <v>7</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D103" s="8">
-        <v>46067.906875000001</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E103" s="8">
-        <v>46067.906875000001</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I103" s="7">
-        <v>1411991</v>
+        <v>1402956</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M103" s="10"/>
       <c r="N103" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O103" s="7"/>
     </row>
@@ -5114,38 +5117,38 @@
         <v>7</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D104" s="8">
-        <v>46069.700543981482</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E104" s="8">
-        <v>46069.700543981482</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I104" s="7">
-        <v>1411991</v>
+        <v>1404958</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="M104" s="10"/>
       <c r="N104" s="10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O104" s="7"/>
     </row>
@@ -5155,34 +5158,34 @@
         <v>7</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D105" s="8">
-        <v>46077.65824074074</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E105" s="8">
-        <v>46077.65824074074</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I105" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M105" s="10"/>
       <c r="N105" s="10">
@@ -5196,38 +5199,38 @@
         <v>7</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D106" s="8">
-        <v>46078.881018518521</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E106" s="8">
-        <v>46078.881018518521</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I106" s="7">
-        <v>1423123</v>
+        <v>1412987</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>83</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M106" s="10"/>
       <c r="N106" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O106" s="7"/>
     </row>
@@ -5237,87 +5240,251 @@
         <v>7</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D107" s="8">
-        <v>46079.901782407411</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="E107" s="8">
-        <v>46079.901782407411</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I107" s="7">
-        <v>1423123</v>
+        <v>1411991</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10">
+        <v>3</v>
+      </c>
+      <c r="O107" s="7"/>
+    </row>
+    <row r="108" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A108" s="2"/>
+      <c r="B108" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D108" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="E108" s="8">
+        <v>46069.700543981482</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I108" s="7">
+        <v>1411991</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="K108" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L108" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="M108" s="10"/>
+      <c r="N108" s="10">
+        <v>10</v>
+      </c>
+      <c r="O108" s="7"/>
+    </row>
+    <row r="109" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A109" s="2"/>
+      <c r="B109" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E109" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I109" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K109" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L109" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M109" s="10"/>
+      <c r="N109" s="10">
         <v>1</v>
       </c>
-      <c r="O107" s="7"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A108" s="4"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="9">
+      <c r="O109" s="7"/>
+    </row>
+    <row r="110" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A110" s="2"/>
+      <c r="B110" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D110" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E110" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I110" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K110" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L110" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M110" s="10"/>
+      <c r="N110" s="10">
+        <v>1</v>
+      </c>
+      <c r="O110" s="7"/>
+    </row>
+    <row r="111" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A111" s="2"/>
+      <c r="B111" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D111" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E111" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I111" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K111" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="L111" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="M111" s="10"/>
+      <c r="N111" s="10">
+        <v>1</v>
+      </c>
+      <c r="O111" s="7"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A112" s="4"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="9">
         <v>0</v>
       </c>
-      <c r="N108" s="9">
-        <v>249</v>
-      </c>
-      <c r="O108" s="9">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A109" s="4"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="9">
-        <v>102</v>
-      </c>
-      <c r="I109" s="6"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
-      <c r="M109" s="9">
+      <c r="N112" s="9">
+        <v>259</v>
+      </c>
+      <c r="O112" s="9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A113" s="4"/>
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+      <c r="G113" s="6"/>
+      <c r="H113" s="9">
+        <v>106</v>
+      </c>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6"/>
+      <c r="K113" s="6"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="9">
         <v>0</v>
       </c>
-      <c r="N109" s="9">
-        <v>491</v>
-      </c>
-      <c r="O109" s="9">
-        <v>102</v>
+      <c r="N113" s="9">
+        <v>509</v>
+      </c>
+      <c r="O113" s="9">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -5327,7 +5494,7 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B61:O61"/>
+    <mergeCell ref="B64:O64"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>

--- a/rejeito.xlsx
+++ b/rejeito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLANILHAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0903554-4587-48B6-9CDA-69D4BBD6EFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53DA3E7D-DAE1-438A-9DCE-F8712E642205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDC75864-2D3A-426D-8A84-ED2527537ED9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B35C81B0-7A14-47F9-9584-254F29B90B35}"/>
   </bookViews>
   <sheets>
     <sheet name="rejeito" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="126">
   <si>
     <t>Dados</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
   </si>
   <si>
     <t>22/01/2026</t>
@@ -939,8 +942,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{874E1856-81A4-4324-B49F-EF2BFD955075}">
-  <dimension ref="A1:O113"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C4202CE-6E87-4D4B-AF2E-AB9D9B0A5A82}">
+  <dimension ref="A1:O116"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -971,14 +974,14 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="M1" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
@@ -992,40 +995,40 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1064,25 +1067,25 @@
         <v>46046.443344907406</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I4" s="7">
         <v>1406207</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M4" s="10"/>
       <c r="N4" s="10">
@@ -1105,25 +1108,25 @@
         <v>46046.553217592591</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I5" s="7">
         <v>1406207</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M5" s="10"/>
       <c r="N5" s="10">
@@ -1146,25 +1149,25 @@
         <v>46050.493333333332</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" s="7">
         <v>1411349</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1187,25 +1190,25 @@
         <v>46051.555428240739</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" s="7">
         <v>1411348</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1228,25 +1231,25 @@
         <v>46053.377129629633</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" s="7">
         <v>1409954</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1269,25 +1272,25 @@
         <v>46062.302418981482</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I9" s="7">
         <v>1411984</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1310,25 +1313,25 @@
         <v>46062.570879629631</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I10" s="7">
         <v>1411984</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1351,25 +1354,25 @@
         <v>46064.297777777778</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I11" s="7">
         <v>1411984</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1392,25 +1395,25 @@
         <v>46064.455104166664</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I12" s="7">
         <v>1411990</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1433,25 +1436,25 @@
         <v>46086.442870370367</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I13" s="7">
         <v>1428327</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1474,25 +1477,25 @@
         <v>46028.331469907411</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I14" s="7">
         <v>1402958</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M14" s="10"/>
       <c r="N14" s="10">
@@ -1515,25 +1518,25 @@
         <v>46030.306192129632</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I15" s="7">
         <v>1394721</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M15" s="10"/>
       <c r="N15" s="10">
@@ -1556,25 +1559,25 @@
         <v>46031.443101851852</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I16" s="7">
         <v>1394721</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M16" s="10"/>
       <c r="N16" s="10">
@@ -1597,25 +1600,25 @@
         <v>46035.530381944445</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I17" s="7">
         <v>1394721</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1638,25 +1641,25 @@
         <v>46046.391701388886</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I18" s="7">
         <v>1410340</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1679,25 +1682,25 @@
         <v>46046.516597222224</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I19" s="7">
         <v>1410340</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1720,25 +1723,25 @@
         <v>46048.278912037036</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I20" s="7">
         <v>1410340</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1761,25 +1764,25 @@
         <v>46051.403391203705</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I21" s="7">
         <v>1410340</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1802,25 +1805,25 @@
         <v>46053.550381944442</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I22" s="7">
         <v>1411706</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1843,25 +1846,25 @@
         <v>46057.413171296299</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I23" s="7">
         <v>1411704</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1884,25 +1887,25 @@
         <v>46058.357476851852</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I24" s="7">
         <v>1411704</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1925,25 +1928,25 @@
         <v>46058.531793981485</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I25" s="7">
         <v>1411704</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -1966,25 +1969,25 @@
         <v>46067.433020833334</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I26" s="7">
         <v>1418256</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -2007,25 +2010,25 @@
         <v>46073.579664351855</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I27" s="7">
         <v>1422511</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2048,25 +2051,25 @@
         <v>46077.38318287037</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I28" s="7">
         <v>1422511</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2089,25 +2092,25 @@
         <v>46078.372766203705</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I29" s="7">
         <v>1422511</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2130,25 +2133,25 @@
         <v>46083.272581018522</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I30" s="7">
         <v>1423124</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2171,25 +2174,25 @@
         <v>46085.323807870373</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I31" s="7">
         <v>1428373</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2212,25 +2215,25 @@
         <v>46085.344675925924</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I32" s="7">
         <v>1428373</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2253,25 +2256,25 @@
         <v>46086.434641203705</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I33" s="7">
         <v>1428373</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2294,25 +2297,25 @@
         <v>46027.4840625</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I34" s="7">
         <v>1404289</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2335,25 +2338,25 @@
         <v>46030.397997685184</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I35" s="7">
         <v>1394724</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2376,25 +2379,25 @@
         <v>46030.408148148148</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I36" s="7">
         <v>1394724</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2417,25 +2420,25 @@
         <v>46030.478854166664</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I37" s="7">
         <v>1394724</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
@@ -2458,25 +2461,25 @@
         <v>46030.561284722222</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I38" s="7">
         <v>1394724</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M38" s="10"/>
       <c r="N38" s="10">
@@ -2499,25 +2502,25 @@
         <v>46035.478368055556</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I39" s="7">
         <v>1394724</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M39" s="10"/>
       <c r="N39" s="10">
@@ -2540,25 +2543,25 @@
         <v>46043.385474537034</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I40" s="7">
         <v>1394724</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M40" s="10"/>
       <c r="N40" s="10">
@@ -2581,25 +2584,25 @@
         <v>46043.565196759257</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I41" s="7">
         <v>1394724</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M41" s="10"/>
       <c r="N41" s="10">
@@ -2622,25 +2625,25 @@
         <v>46069.559953703705</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I42" s="7">
         <v>1421099</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M42" s="10"/>
       <c r="N42" s="10">
@@ -2663,25 +2666,25 @@
         <v>46078.552407407406</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I43" s="7">
         <v>1422286</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M43" s="10"/>
       <c r="N43" s="10">
@@ -2704,25 +2707,25 @@
         <v>46080.522418981483</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I44" s="7">
         <v>1422285</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M44" s="10"/>
       <c r="N44" s="10">
@@ -2745,25 +2748,25 @@
         <v>46080.532164351855</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I45" s="7">
         <v>1422285</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M45" s="10"/>
       <c r="N45" s="10">
@@ -2786,25 +2789,25 @@
         <v>46083.531342592592</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I46" s="7">
         <v>1422283</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2827,25 +2830,25 @@
         <v>46085.365902777776</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I47" s="7">
         <v>1422283</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
@@ -2868,25 +2871,25 @@
         <v>46086.317847222221</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I48" s="7">
         <v>1428242</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
@@ -2897,78 +2900,78 @@
     <row r="49" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D49" s="8">
-        <v>46035.47824074074</v>
+        <v>46087.292048611111</v>
       </c>
       <c r="E49" s="8">
-        <v>46035.47824074074</v>
+        <v>46087.292048611111</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I49" s="7">
-        <v>1404958</v>
+        <v>1422282</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O49" s="7"/>
     </row>
     <row r="50" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D50" s="8">
-        <v>46043.385196759256</v>
+        <v>46087.575972222221</v>
       </c>
       <c r="E50" s="8">
-        <v>46043.385196759256</v>
+        <v>46087.575972222221</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I50" s="7">
-        <v>1405794</v>
+        <v>1422282</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
@@ -2982,38 +2985,38 @@
         <v>7</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D51" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="E51" s="8">
-        <v>46043.385289351849</v>
+        <v>46035.47824074074</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>58</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I51" s="7">
-        <v>1405794</v>
+        <v>1404958</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>98</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O51" s="7"/>
     </row>
@@ -3026,35 +3029,35 @@
         <v>31</v>
       </c>
       <c r="D52" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="E52" s="8">
-        <v>46043.441296296296</v>
+        <v>46043.385196759256</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I52" s="7">
         <v>1405794</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O52" s="7"/>
     </row>
@@ -3064,34 +3067,34 @@
         <v>7</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D53" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="E53" s="8">
-        <v>46044.570300925923</v>
+        <v>46043.385289351849</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I53" s="7">
         <v>1405794</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
@@ -3105,38 +3108,38 @@
         <v>7</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D54" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="E54" s="8">
-        <v>46050.574884259258</v>
+        <v>46043.441296296296</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>56</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I54" s="7">
-        <v>1411351</v>
+        <v>1405794</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O54" s="7"/>
     </row>
@@ -3146,38 +3149,38 @@
         <v>7</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="D55" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="E55" s="8">
-        <v>46051.280300925922</v>
+        <v>46044.570300925923</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I55" s="7">
-        <v>1411352</v>
+        <v>1405794</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M55" s="10"/>
       <c r="N55" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O55" s="7"/>
     </row>
@@ -3187,38 +3190,38 @@
         <v>7</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D56" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="E56" s="8">
-        <v>46056.33489583333</v>
+        <v>46050.574884259258</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I56" s="7">
-        <v>1410338</v>
+        <v>1411351</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M56" s="10"/>
       <c r="N56" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O56" s="7"/>
     </row>
@@ -3228,38 +3231,38 @@
         <v>7</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D57" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="E57" s="8">
-        <v>46062.345243055555</v>
+        <v>46051.280300925922</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I57" s="7">
-        <v>1412987</v>
+        <v>1411352</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="M57" s="10"/>
       <c r="N57" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O57" s="7"/>
     </row>
@@ -3269,38 +3272,38 @@
         <v>7</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D58" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="E58" s="8">
-        <v>46064.292500000003</v>
+        <v>46056.33489583333</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I58" s="7">
-        <v>1412987</v>
+        <v>1410338</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M58" s="10"/>
       <c r="N58" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O58" s="7"/>
     </row>
@@ -3310,38 +3313,38 @@
         <v>7</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D59" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="E59" s="8">
-        <v>46073.402627314812</v>
+        <v>46062.345243055555</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I59" s="7">
-        <v>1421099</v>
+        <v>1412987</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M59" s="10"/>
       <c r="N59" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O59" s="7"/>
     </row>
@@ -3351,34 +3354,34 @@
         <v>7</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D60" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="E60" s="8">
-        <v>46077.368379629632</v>
+        <v>46064.292500000003</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I60" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M60" s="10"/>
       <c r="N60" s="10">
@@ -3392,38 +3395,38 @@
         <v>7</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D61" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="E61" s="8">
-        <v>46077.554594907408</v>
+        <v>46073.402627314812</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I61" s="7">
-        <v>1422285</v>
+        <v>1421099</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M61" s="10"/>
       <c r="N61" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O61" s="7"/>
     </row>
@@ -3433,166 +3436,166 @@
         <v>7</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D62" s="8">
-        <v>46085.366041666668</v>
+        <v>46077.368379629632</v>
       </c>
       <c r="E62" s="8">
-        <v>46085.366041666668</v>
+        <v>46077.368379629632</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I62" s="7">
-        <v>1423125</v>
+        <v>1422285</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M62" s="10"/>
       <c r="N62" s="10">
+        <v>3</v>
+      </c>
+      <c r="O62" s="7"/>
+    </row>
+    <row r="63" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A63" s="2"/>
+      <c r="B63" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="E63" s="8">
+        <v>46077.554594907408</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I63" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10">
+        <v>3</v>
+      </c>
+      <c r="O63" s="7"/>
+    </row>
+    <row r="64" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A64" s="2"/>
+      <c r="B64" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="8">
+        <v>46085.366041666668</v>
+      </c>
+      <c r="E64" s="8">
+        <v>46085.366041666668</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I64" s="7">
+        <v>1423125</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10">
         <v>5</v>
       </c>
-      <c r="O62" s="7"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A63" s="4"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="9">
+      <c r="O64" s="7"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A65" s="4"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="9">
         <v>0</v>
       </c>
-      <c r="N63" s="9">
-        <v>250</v>
-      </c>
-      <c r="O63" s="9">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="3" t="s">
+      <c r="N65" s="9">
+        <v>260</v>
+      </c>
+      <c r="O65" s="9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B66" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="12"/>
-      <c r="M64" s="12"/>
-      <c r="N64" s="12"/>
-      <c r="O64" s="12"/>
-    </row>
-    <row r="65" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A65" s="2"/>
-      <c r="B65" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D65" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="E65" s="8">
-        <v>46027.666331018518</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I65" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="K65" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="L65" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10">
-        <v>3</v>
-      </c>
-      <c r="O65" s="7"/>
-    </row>
-    <row r="66" spans="1:15" ht="21" x14ac:dyDescent="0.2">
-      <c r="A66" s="2"/>
-      <c r="B66" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D66" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="E66" s="8">
-        <v>46027.694131944445</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I66" s="7">
-        <v>1386388</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="L66" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10">
-        <v>1</v>
-      </c>
-      <c r="O66" s="7"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
     </row>
     <row r="67" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
@@ -3600,38 +3603,38 @@
         <v>4</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D67" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="E67" s="8">
-        <v>46036.841574074075</v>
+        <v>46027.666331018518</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I67" s="7">
-        <v>1406206</v>
+        <v>1386388</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="M67" s="10"/>
       <c r="N67" s="10">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O67" s="7"/>
     </row>
@@ -3641,38 +3644,38 @@
         <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D68" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="E68" s="8">
-        <v>46059.905682870369</v>
+        <v>46027.694131944445</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I68" s="7">
-        <v>1411984</v>
+        <v>1386388</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M68" s="10"/>
       <c r="N68" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O68" s="7"/>
     </row>
@@ -3682,38 +3685,38 @@
         <v>4</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D69" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="E69" s="8">
-        <v>46064.60796296296</v>
+        <v>46036.841574074075</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I69" s="7">
-        <v>1411990</v>
+        <v>1406206</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M69" s="10"/>
       <c r="N69" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O69" s="7"/>
     </row>
@@ -3726,35 +3729,35 @@
         <v>38</v>
       </c>
       <c r="D70" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="E70" s="8">
-        <v>46065.655185185184</v>
+        <v>46059.905682870369</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I70" s="7">
-        <v>1411990</v>
+        <v>1411984</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M70" s="10"/>
       <c r="N70" s="10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O70" s="7"/>
     </row>
@@ -3764,38 +3767,38 @@
         <v>4</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D71" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="E71" s="8">
-        <v>46066.613657407404</v>
+        <v>46064.60796296296</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I71" s="7">
         <v>1411990</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M71" s="10"/>
       <c r="N71" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" s="7"/>
     </row>
@@ -3808,31 +3811,31 @@
         <v>39</v>
       </c>
       <c r="D72" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="E72" s="8">
-        <v>46066.670127314814</v>
+        <v>46065.655185185184</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I72" s="7">
         <v>1411990</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M72" s="10"/>
       <c r="N72" s="10">
@@ -3849,35 +3852,35 @@
         <v>40</v>
       </c>
       <c r="D73" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="E73" s="8">
-        <v>46079.703912037039</v>
+        <v>46066.613657407404</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I73" s="7">
-        <v>1410767</v>
+        <v>1411990</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M73" s="10"/>
       <c r="N73" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O73" s="7"/>
     </row>
@@ -3887,38 +3890,38 @@
         <v>4</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D74" s="8">
-        <v>46084.877986111111</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="E74" s="8">
-        <v>46084.877986111111</v>
+        <v>46066.670127314814</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I74" s="7">
-        <v>1428327</v>
+        <v>1411990</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M74" s="10"/>
       <c r="N74" s="10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O74" s="7"/>
     </row>
@@ -3931,117 +3934,117 @@
         <v>41</v>
       </c>
       <c r="D75" s="8">
-        <v>46084.883263888885</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="E75" s="8">
-        <v>46084.883263888885</v>
+        <v>46079.703912037039</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I75" s="7">
-        <v>1428327</v>
+        <v>1410767</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M75" s="10"/>
       <c r="N75" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O75" s="7"/>
     </row>
     <row r="76" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D76" s="8">
-        <v>46028.907905092594</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="E76" s="8">
-        <v>46028.907905092594</v>
+        <v>46084.877986111111</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I76" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J76" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M76" s="10"/>
       <c r="N76" s="10">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="O76" s="7"/>
     </row>
     <row r="77" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>42</v>
       </c>
       <c r="D77" s="8">
-        <v>46029.6719212963</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="E77" s="8">
-        <v>46029.6719212963</v>
+        <v>46084.883263888885</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I77" s="7">
-        <v>1394721</v>
+        <v>1428327</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M77" s="10"/>
       <c r="N77" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O77" s="7"/>
     </row>
@@ -4051,38 +4054,38 @@
         <v>5</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D78" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="E78" s="8">
-        <v>46034.72855324074</v>
+        <v>46028.907905092594</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I78" s="7">
         <v>1394721</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M78" s="10"/>
       <c r="N78" s="10">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O78" s="7"/>
     </row>
@@ -4092,38 +4095,38 @@
         <v>5</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D79" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="E79" s="8">
-        <v>46037.838958333334</v>
+        <v>46029.6719212963</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I79" s="7">
         <v>1394721</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M79" s="10"/>
       <c r="N79" s="10">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O79" s="7"/>
     </row>
@@ -4133,38 +4136,38 @@
         <v>5</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D80" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="E80" s="8">
-        <v>46042.727754629632</v>
+        <v>46034.72855324074</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I80" s="7">
         <v>1394721</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M80" s="10"/>
       <c r="N80" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O80" s="7"/>
     </row>
@@ -4174,38 +4177,38 @@
         <v>5</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D81" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="E81" s="8">
-        <v>46043.627881944441</v>
+        <v>46037.838958333334</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I81" s="7">
-        <v>1410339</v>
+        <v>1394721</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M81" s="10"/>
       <c r="N81" s="10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O81" s="7"/>
     </row>
@@ -4218,35 +4221,35 @@
         <v>46</v>
       </c>
       <c r="D82" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="E82" s="8">
-        <v>46052.626018518517</v>
+        <v>46042.727754629632</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I82" s="7">
-        <v>1411706</v>
+        <v>1394721</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>86</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M82" s="10"/>
       <c r="N82" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O82" s="7"/>
     </row>
@@ -4256,38 +4259,38 @@
         <v>5</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D83" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="E83" s="8">
-        <v>46053.632291666669</v>
+        <v>46043.627881944441</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I83" s="7">
-        <v>1411708</v>
+        <v>1410339</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>103</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M83" s="10"/>
       <c r="N83" s="10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O83" s="7"/>
     </row>
@@ -4300,35 +4303,35 @@
         <v>47</v>
       </c>
       <c r="D84" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="E84" s="8">
-        <v>46071.601446759261</v>
+        <v>46052.626018518517</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I84" s="7">
-        <v>1418251</v>
+        <v>1411706</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M84" s="10"/>
       <c r="N84" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O84" s="7"/>
     </row>
@@ -4338,38 +4341,38 @@
         <v>5</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D85" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="E85" s="8">
-        <v>46076.679282407407</v>
+        <v>46053.632291666669</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>64</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I85" s="7">
-        <v>1422511</v>
+        <v>1411708</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M85" s="10"/>
       <c r="N85" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O85" s="7"/>
     </row>
@@ -4379,38 +4382,38 @@
         <v>5</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D86" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="E86" s="8">
-        <v>46077.591944444444</v>
+        <v>46071.601446759261</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I86" s="7">
-        <v>1422511</v>
+        <v>1418251</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M86" s="10"/>
       <c r="N86" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O86" s="7"/>
     </row>
@@ -4420,38 +4423,38 @@
         <v>5</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D87" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="E87" s="8">
-        <v>46077.861296296294</v>
+        <v>46076.679282407407</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I87" s="7">
         <v>1422511</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M87" s="10"/>
       <c r="N87" s="10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O87" s="7"/>
     </row>
@@ -4461,116 +4464,116 @@
         <v>5</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D88" s="8">
-        <v>46086.860844907409</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="E88" s="8">
-        <v>46086.860844907409</v>
+        <v>46077.591944444444</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I88" s="7">
-        <v>1428373</v>
+        <v>1422511</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M88" s="10"/>
       <c r="N88" s="10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="O88" s="7"/>
     </row>
     <row r="89" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D89" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="E89" s="8">
-        <v>46027.633611111109</v>
+        <v>46077.861296296294</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I89" s="7">
-        <v>1404289</v>
+        <v>1422511</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M89" s="10"/>
       <c r="N89" s="10">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O89" s="7"/>
     </row>
     <row r="90" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D90" s="8">
-        <v>46029.802372685182</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="E90" s="8">
-        <v>46029.802372685182</v>
+        <v>46086.860844907409</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I90" s="7">
-        <v>1394724</v>
+        <v>1428373</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K90" s="5" t="s">
         <v>111</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M90" s="10"/>
       <c r="N90" s="10">
@@ -4584,38 +4587,38 @@
         <v>6</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D91" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="E91" s="8">
-        <v>46030.908472222225</v>
+        <v>46027.633611111109</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H91" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I91" s="7">
-        <v>1394724</v>
+        <v>1404289</v>
       </c>
       <c r="J91" s="5" t="s">
         <v>93</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M91" s="10"/>
       <c r="N91" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O91" s="7"/>
     </row>
@@ -4625,19 +4628,19 @@
         <v>6</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D92" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="E92" s="8">
-        <v>46031.590057870373</v>
+        <v>46029.802372685182</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>76</v>
@@ -4646,17 +4649,17 @@
         <v>1394724</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M92" s="10"/>
       <c r="N92" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O92" s="7"/>
     </row>
@@ -4666,38 +4669,38 @@
         <v>6</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D93" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="E93" s="8">
-        <v>46076.8827662037</v>
+        <v>46030.908472222225</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I93" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M93" s="10"/>
       <c r="N93" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O93" s="7"/>
     </row>
@@ -4707,34 +4710,34 @@
         <v>6</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D94" s="8">
-        <v>46078.867326388892</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="E94" s="8">
-        <v>46078.867326388892</v>
+        <v>46031.590057870373</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I94" s="7">
-        <v>1422286</v>
+        <v>1394724</v>
       </c>
       <c r="J94" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M94" s="10"/>
       <c r="N94" s="10">
@@ -4748,38 +4751,38 @@
         <v>6</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D95" s="8">
-        <v>46080.639293981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="E95" s="8">
-        <v>46080.639293981483</v>
+        <v>46076.8827662037</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I95" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J95" s="5" t="s">
         <v>96</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L95" s="7" t="s">
         <v>118</v>
       </c>
       <c r="M95" s="10"/>
       <c r="N95" s="10">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O95" s="7"/>
     </row>
@@ -4789,38 +4792,38 @@
         <v>6</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D96" s="8">
-        <v>46080.716932870368</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="E96" s="8">
-        <v>46080.716932870368</v>
+        <v>46078.867326388892</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I96" s="7">
-        <v>1422285</v>
+        <v>1422286</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>96</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L96" s="7" t="s">
         <v>118</v>
       </c>
       <c r="M96" s="10"/>
       <c r="N96" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O96" s="7"/>
     </row>
@@ -4833,35 +4836,35 @@
         <v>33</v>
       </c>
       <c r="D97" s="8">
-        <v>46080.740543981483</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="E97" s="8">
-        <v>46080.740543981483</v>
+        <v>46080.639293981483</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I97" s="7">
         <v>1422285</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M97" s="10"/>
       <c r="N97" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O97" s="7"/>
     </row>
@@ -4871,34 +4874,34 @@
         <v>6</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D98" s="8">
-        <v>46081.588483796295</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="E98" s="8">
-        <v>46081.588483796295</v>
+        <v>46080.716932870368</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I98" s="7">
         <v>1422285</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M98" s="10"/>
       <c r="N98" s="10">
@@ -4912,161 +4915,161 @@
         <v>6</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D99" s="8">
-        <v>46083.87841435185</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="E99" s="8">
-        <v>46083.87841435185</v>
+        <v>46080.740543981483</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I99" s="7">
-        <v>1422283</v>
+        <v>1422285</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="M99" s="10"/>
       <c r="N99" s="10">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="O99" s="7"/>
     </row>
     <row r="100" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>50</v>
       </c>
       <c r="D100" s="8">
-        <v>46024.795127314814</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="E100" s="8">
-        <v>46024.795127314814</v>
+        <v>46081.588483796295</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I100" s="7">
-        <v>1398335</v>
+        <v>1422285</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="M100" s="10"/>
       <c r="N100" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O100" s="7"/>
     </row>
     <row r="101" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D101" s="8">
-        <v>46024.795277777775</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="E101" s="8">
-        <v>46024.795277777775</v>
+        <v>46083.87841435185</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I101" s="7">
-        <v>1398335</v>
+        <v>1422283</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M101" s="10"/>
       <c r="N101" s="10">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O101" s="7"/>
     </row>
     <row r="102" spans="1:15" ht="21" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D102" s="8">
-        <v>46024.900324074071</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="E102" s="8">
-        <v>46024.900324074071</v>
+        <v>46087.689409722225</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H102" s="5" t="s">
         <v>76</v>
       </c>
       <c r="I102" s="7">
-        <v>1398335</v>
+        <v>1422282</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="M102" s="10"/>
       <c r="N102" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O102" s="7"/>
     </row>
@@ -5076,38 +5079,38 @@
         <v>7</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D103" s="8">
-        <v>46028.866898148146</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="E103" s="8">
-        <v>46028.866898148146</v>
+        <v>46024.795127314814</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I103" s="7">
-        <v>1402956</v>
+        <v>1398335</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M103" s="10"/>
       <c r="N103" s="10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O103" s="7"/>
     </row>
@@ -5117,38 +5120,38 @@
         <v>7</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D104" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="E104" s="8">
-        <v>46034.751261574071</v>
+        <v>46024.795277777775</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I104" s="7">
-        <v>1404958</v>
+        <v>1398335</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M104" s="10"/>
       <c r="N104" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O104" s="7"/>
     </row>
@@ -5158,38 +5161,38 @@
         <v>7</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D105" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="E105" s="8">
-        <v>46062.904895833337</v>
+        <v>46024.900324074071</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I105" s="7">
-        <v>1412987</v>
+        <v>1398335</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M105" s="10"/>
       <c r="N105" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O105" s="7"/>
     </row>
@@ -5199,38 +5202,38 @@
         <v>7</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="D106" s="8">
-        <v>46063.874467592592</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="E106" s="8">
-        <v>46063.874467592592</v>
+        <v>46028.866898148146</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I106" s="7">
-        <v>1412987</v>
+        <v>1402956</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M106" s="10"/>
       <c r="N106" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O106" s="7"/>
     </row>
@@ -5240,38 +5243,38 @@
         <v>7</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D107" s="8">
-        <v>46067.906875000001</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="E107" s="8">
-        <v>46067.906875000001</v>
+        <v>46034.751261574071</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I107" s="7">
-        <v>1411991</v>
+        <v>1404958</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="M107" s="10"/>
       <c r="N107" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O107" s="7"/>
     </row>
@@ -5281,38 +5284,38 @@
         <v>7</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D108" s="8">
-        <v>46069.700543981482</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="E108" s="8">
-        <v>46069.700543981482</v>
+        <v>46062.904895833337</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I108" s="7">
-        <v>1411991</v>
+        <v>1412987</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="M108" s="10"/>
       <c r="N108" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O108" s="7"/>
     </row>
@@ -5322,38 +5325,38 @@
         <v>7</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D109" s="8">
-        <v>46077.65824074074</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="E109" s="8">
-        <v>46077.65824074074</v>
+        <v>46063.874467592592</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I109" s="7">
-        <v>1422285</v>
+        <v>1412987</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="K109" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M109" s="10"/>
       <c r="N109" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O109" s="7"/>
     </row>
@@ -5363,38 +5366,38 @@
         <v>7</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D110" s="8">
-        <v>46078.881018518521</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="E110" s="8">
-        <v>46078.881018518521</v>
+        <v>46067.906875000001</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I110" s="7">
-        <v>1423123</v>
+        <v>1411991</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L110" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M110" s="10"/>
       <c r="N110" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O110" s="7"/>
     </row>
@@ -5404,87 +5407,210 @@
         <v>7</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D111" s="8">
-        <v>46079.901782407411</v>
+        <v>46069.700543981482</v>
       </c>
       <c r="E111" s="8">
-        <v>46079.901782407411</v>
+        <v>46069.700543981482</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I111" s="7">
-        <v>1423123</v>
+        <v>1411991</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M111" s="10"/>
       <c r="N111" s="10">
+        <v>10</v>
+      </c>
+      <c r="O111" s="7"/>
+    </row>
+    <row r="112" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A112" s="2"/>
+      <c r="B112" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D112" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="E112" s="8">
+        <v>46077.65824074074</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I112" s="7">
+        <v>1422285</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L112" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="M112" s="10"/>
+      <c r="N112" s="10">
         <v>1</v>
       </c>
-      <c r="O111" s="7"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A112" s="4"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
-      <c r="M112" s="9">
+      <c r="O112" s="7"/>
+    </row>
+    <row r="113" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A113" s="2"/>
+      <c r="B113" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="E113" s="8">
+        <v>46078.881018518521</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H113" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I113" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K113" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L113" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M113" s="10"/>
+      <c r="N113" s="10">
+        <v>1</v>
+      </c>
+      <c r="O113" s="7"/>
+    </row>
+    <row r="114" spans="1:15" ht="21" x14ac:dyDescent="0.2">
+      <c r="A114" s="2"/>
+      <c r="B114" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D114" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="E114" s="8">
+        <v>46079.901782407411</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I114" s="7">
+        <v>1423123</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K114" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="L114" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="M114" s="10"/>
+      <c r="N114" s="10">
+        <v>1</v>
+      </c>
+      <c r="O114" s="7"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A115" s="4"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="9">
         <v>0</v>
       </c>
-      <c r="N112" s="9">
-        <v>259</v>
-      </c>
-      <c r="O112" s="9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A113" s="4"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="9">
-        <v>106</v>
-      </c>
-      <c r="I113" s="6"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
-      <c r="M113" s="9">
+      <c r="N115" s="9">
+        <v>267</v>
+      </c>
+      <c r="O115" s="9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A116" s="4"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
+      <c r="H116" s="9">
+        <v>109</v>
+      </c>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6"/>
+      <c r="K116" s="6"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="9">
         <v>0</v>
       </c>
-      <c r="N113" s="9">
-        <v>509</v>
-      </c>
-      <c r="O113" s="9">
-        <v>106</v>
+      <c r="N116" s="9">
+        <v>527</v>
+      </c>
+      <c r="O116" s="9">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5494,7 +5620,7 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B64:O64"/>
+    <mergeCell ref="B66:O66"/>
   </mergeCells>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
 </worksheet>
